--- a/nursery_monitoring/GB monitoring.xlsx
+++ b/nursery_monitoring/GB monitoring.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1518" uniqueCount="81">
   <si>
     <t>Date</t>
   </si>
@@ -268,7 +268,7 @@
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -283,6 +283,7 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
+    <font/>
   </fonts>
   <fills count="3">
     <fill>
@@ -304,7 +305,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -345,6 +346,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -574,7 +578,8 @@
   <cols>
     <col customWidth="1" min="3" max="3" width="10.71"/>
     <col customWidth="1" min="4" max="4" width="12.0"/>
-    <col hidden="1" min="5" max="6" width="14.43"/>
+    <col customWidth="1" min="9" max="9" width="18.0"/>
+    <col customWidth="1" min="10" max="10" width="15.14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11483,280 +11488,2364 @@
       </c>
     </row>
     <row r="462">
-      <c r="I462" s="5"/>
+      <c r="A462" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B462" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C462" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D462" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G462" s="4">
+        <v>8.0</v>
+      </c>
+      <c r="H462" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="I462" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J462" s="4">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="463">
-      <c r="I463" s="5"/>
+      <c r="A463" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B463" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C463" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D463" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G463" s="4">
+        <v>14.5</v>
+      </c>
+      <c r="H463" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="I463" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J463" s="4">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="464">
-      <c r="I464" s="5"/>
+      <c r="A464" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B464" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C464" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D464" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G464" s="4">
+        <v>8.5</v>
+      </c>
+      <c r="H464" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="I464" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J464" s="4">
+        <v>5.0</v>
+      </c>
     </row>
     <row r="465">
-      <c r="I465" s="5"/>
+      <c r="A465" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B465" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C465" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D465" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G465" s="4">
+        <v>16.5</v>
+      </c>
+      <c r="H465" s="4">
+        <v>9.0</v>
+      </c>
+      <c r="I465" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J465" s="4">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="466">
-      <c r="I466" s="5"/>
+      <c r="A466" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B466" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C466" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D466" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="G466" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H466" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="I466" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J466" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="467">
-      <c r="I467" s="5"/>
+      <c r="A467" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B467" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C467" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D467" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G467" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="H467" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="I467" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J467" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="468">
-      <c r="I468" s="5"/>
+      <c r="A468" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B468" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C468" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D468" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G468" s="4">
+        <v>11.0</v>
+      </c>
+      <c r="H468" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="I468" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J468" s="4">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="469">
-      <c r="I469" s="5"/>
+      <c r="A469" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B469" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C469" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D469" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G469" s="4">
+        <v>8.0</v>
+      </c>
+      <c r="H469" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="I469" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J469" s="4">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="470">
-      <c r="I470" s="5"/>
+      <c r="A470" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B470" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C470" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D470" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G470" s="4">
+        <v>15.0</v>
+      </c>
+      <c r="H470" s="4">
+        <v>9.0</v>
+      </c>
+      <c r="I470" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J470" s="4">
+        <v>6.0</v>
+      </c>
     </row>
     <row r="471">
-      <c r="I471" s="5"/>
+      <c r="A471" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B471" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C471" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D471" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G471" s="4">
+        <v>13.5</v>
+      </c>
+      <c r="H471" s="4">
+        <v>8.0</v>
+      </c>
+      <c r="I471" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J471" s="4">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="472">
-      <c r="I472" s="5"/>
+      <c r="A472" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B472" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C472" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D472" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G472" s="4">
+        <v>16.5</v>
+      </c>
+      <c r="H472" s="4">
+        <v>9.0</v>
+      </c>
+      <c r="I472" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J472" s="4">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="473">
-      <c r="I473" s="5"/>
+      <c r="A473" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B473" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C473" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D473" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G473" s="4">
+        <v>13.0</v>
+      </c>
+      <c r="H473" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="I473" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J473" s="4">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="474">
-      <c r="I474" s="5"/>
+      <c r="A474" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B474" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C474" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D474" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="F474" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I474" s="8"/>
     </row>
     <row r="475">
-      <c r="I475" s="5"/>
+      <c r="A475" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B475" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C475" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D475" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G475" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="H475" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="I475" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J475" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="476">
-      <c r="I476" s="5"/>
+      <c r="A476" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B476" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C476" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D476" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="G476" s="4">
+        <v>12.5</v>
+      </c>
+      <c r="H476" s="4">
+        <v>9.0</v>
+      </c>
+      <c r="I476" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J476" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="477">
-      <c r="I477" s="5"/>
+      <c r="A477" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B477" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C477" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D477" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="G477" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="H477" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="I477" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J477" s="4">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="478">
-      <c r="I478" s="5"/>
+      <c r="A478" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B478" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C478" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D478" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G478" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="H478" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="I478" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J478" s="4">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="479">
-      <c r="I479" s="5"/>
+      <c r="A479" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B479" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C479" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D479" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G479" s="4">
+        <v>8.0</v>
+      </c>
+      <c r="H479" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="I479" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J479" s="4">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="480">
-      <c r="I480" s="5"/>
+      <c r="A480" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B480" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C480" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D480" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G480" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H480" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="I480" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J480" s="4">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="481">
-      <c r="I481" s="5"/>
+      <c r="A481" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B481" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C481" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D481" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G481" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H481" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="I481" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J481" s="4">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="482">
-      <c r="I482" s="5"/>
+      <c r="A482" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B482" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C482" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D482" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G482" s="4">
+        <v>6.5</v>
+      </c>
+      <c r="H482" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="I482" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J482" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="483">
-      <c r="I483" s="5"/>
+      <c r="A483" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B483" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C483" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D483" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G483" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="H483" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="I483" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J483" s="4">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="484">
-      <c r="I484" s="5"/>
+      <c r="A484" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B484" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C484" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D484" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G484" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="H484" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="I484" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J484" s="4">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="485">
-      <c r="I485" s="5"/>
+      <c r="A485" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B485" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C485" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D485" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="F485" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I485" s="8"/>
     </row>
     <row r="486">
-      <c r="I486" s="5"/>
+      <c r="A486" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B486" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C486" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D486" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="F486" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I486" s="8"/>
     </row>
     <row r="487">
-      <c r="I487" s="5"/>
+      <c r="A487" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B487" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C487" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D487" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="G487" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="H487" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="I487" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J487" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="488">
-      <c r="I488" s="5"/>
+      <c r="A488" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B488" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C488" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D488" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="G488" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H488" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="I488" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J488" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="489">
-      <c r="I489" s="5"/>
+      <c r="A489" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B489" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C489" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D489" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="F489" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I489" s="8"/>
     </row>
     <row r="490">
-      <c r="I490" s="5"/>
+      <c r="A490" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B490" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C490" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D490" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G490" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H490" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="I490" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J490" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="491">
-      <c r="I491" s="5"/>
+      <c r="A491" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B491" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C491" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D491" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G491" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H491" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="I491" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J491" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="492">
-      <c r="I492" s="5"/>
+      <c r="A492" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B492" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C492" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D492" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G492" s="4">
+        <v>9.5</v>
+      </c>
+      <c r="H492" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="I492" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J492" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="493">
-      <c r="I493" s="5"/>
+      <c r="A493" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B493" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C493" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D493" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G493" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H493" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="I493" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J493" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="494">
-      <c r="I494" s="5"/>
+      <c r="A494" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B494" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C494" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D494" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G494" s="4">
+        <v>9.0</v>
+      </c>
+      <c r="H494" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="I494" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J494" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="495">
-      <c r="I495" s="5"/>
+      <c r="A495" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B495" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C495" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D495" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G495" s="4">
+        <v>9.0</v>
+      </c>
+      <c r="H495" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="I495" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J495" s="4">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="496">
-      <c r="I496" s="5"/>
+      <c r="A496" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B496" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C496" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D496" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="G496" s="4">
+        <v>9.5</v>
+      </c>
+      <c r="H496" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="I496" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J496" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="497">
-      <c r="I497" s="5"/>
+      <c r="A497" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B497" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C497" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D497" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G497" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="H497" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="I497" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J497" s="4">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="498">
-      <c r="I498" s="5"/>
+      <c r="A498" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B498" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C498" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D498" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G498" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="H498" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="I498" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J498" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="499">
-      <c r="I499" s="5"/>
+      <c r="A499" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B499" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C499" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D499" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G499" s="4">
+        <v>9.0</v>
+      </c>
+      <c r="H499" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="I499" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J499" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="500">
-      <c r="I500" s="5"/>
+      <c r="A500" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B500" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C500" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D500" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G500" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="H500" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="I500" s="8">
+        <v>7.0</v>
+      </c>
+      <c r="J500" s="4">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="501">
-      <c r="I501" s="5"/>
+      <c r="A501" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B501" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C501" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D501" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G501" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H501" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="I501" s="8">
+        <v>7.0</v>
+      </c>
+      <c r="J501" s="4">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="502">
-      <c r="I502" s="5"/>
+      <c r="A502" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B502" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C502" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D502" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G502" s="4">
+        <v>6.5</v>
+      </c>
+      <c r="H502" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="I502" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J502" s="4">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="503">
-      <c r="I503" s="5"/>
+      <c r="A503" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B503" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C503" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D503" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G503" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="H503" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="I503" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J503" s="4">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="504">
-      <c r="I504" s="5"/>
+      <c r="A504" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B504" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C504" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D504" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G504" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="H504" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="I504" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J504" s="4">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="505">
-      <c r="I505" s="5"/>
+      <c r="A505" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B505" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C505" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D505" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G505" s="4">
+        <v>9.0</v>
+      </c>
+      <c r="H505" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="I505" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J505" s="4">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="506">
-      <c r="I506" s="5"/>
+      <c r="A506" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B506" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C506" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D506" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G506" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="H506" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="I506" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J506" s="4">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="507">
-      <c r="I507" s="5"/>
+      <c r="A507" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B507" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C507" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D507" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G507" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="H507" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="I507" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J507" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="508">
-      <c r="I508" s="5"/>
+      <c r="A508" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B508" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C508" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D508" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G508" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="H508" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="I508" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J508" s="4">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="509">
-      <c r="I509" s="5"/>
+      <c r="A509" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B509" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C509" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D509" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G509" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="H509" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="I509" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J509" s="4">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="510">
-      <c r="I510" s="5"/>
+      <c r="A510" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B510" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C510" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D510" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G510" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="H510" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="I510" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J510" s="4">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="511">
-      <c r="I511" s="5"/>
+      <c r="A511" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B511" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C511" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D511" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G511" s="4">
+        <v>9.5</v>
+      </c>
+      <c r="H511" s="4">
+        <v>6.5</v>
+      </c>
+      <c r="I511" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J511" s="4">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="512">
-      <c r="I512" s="5"/>
+      <c r="A512" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B512" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C512" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D512" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G512" s="4">
+        <v>11.0</v>
+      </c>
+      <c r="H512" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="I512" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J512" s="4">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="513">
-      <c r="I513" s="5"/>
+      <c r="A513" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B513" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C513" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D513" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G513" s="4">
+        <v>14.0</v>
+      </c>
+      <c r="H513" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="I513" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J513" s="4">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="514">
-      <c r="I514" s="5"/>
+      <c r="A514" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B514" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C514" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D514" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G514" s="4">
+        <v>9.0</v>
+      </c>
+      <c r="H514" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="I514" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J514" s="4">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="515">
-      <c r="I515" s="5"/>
+      <c r="A515" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B515" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C515" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D515" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G515" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="H515" s="4">
+        <v>6.5</v>
+      </c>
+      <c r="I515" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J515" s="4">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="516">
-      <c r="I516" s="5"/>
+      <c r="A516" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B516" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C516" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D516" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G516" s="4">
+        <v>8.5</v>
+      </c>
+      <c r="H516" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="I516" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J516" s="4">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="517">
-      <c r="I517" s="5"/>
+      <c r="A517" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B517" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C517" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D517" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G517" s="4">
+        <v>13.5</v>
+      </c>
+      <c r="H517" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="I517" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J517" s="4">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="518">
-      <c r="I518" s="5"/>
+      <c r="A518" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B518" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C518" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D518" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G518" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="H518" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="I518" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J518" s="4">
+        <v>5.0</v>
+      </c>
     </row>
     <row r="519">
-      <c r="I519" s="5"/>
+      <c r="A519" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B519" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C519" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D519" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G519" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="H519" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="I519" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J519" s="4">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="520">
-      <c r="I520" s="5"/>
+      <c r="A520" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B520" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C520" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D520" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G520" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="H520" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="I520" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J520" s="4">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="521">
-      <c r="I521" s="5"/>
+      <c r="A521" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B521" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C521" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D521" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G521" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="H521" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="I521" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J521" s="4">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="522">
-      <c r="I522" s="5"/>
+      <c r="A522" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B522" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C522" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D522" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G522" s="4">
+        <v>8.0</v>
+      </c>
+      <c r="H522" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="I522" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J522" s="4">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="523">
-      <c r="I523" s="5"/>
+      <c r="A523" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B523" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C523" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D523" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G523" s="4">
+        <v>9.5</v>
+      </c>
+      <c r="H523" s="4">
+        <v>6.5</v>
+      </c>
+      <c r="I523" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J523" s="4">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="524">
-      <c r="I524" s="5"/>
+      <c r="A524" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B524" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C524" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D524" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G524" s="4">
+        <v>11.0</v>
+      </c>
+      <c r="H524" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="I524" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J524" s="4">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="525">
-      <c r="I525" s="5"/>
+      <c r="A525" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B525" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C525" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D525" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G525" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="H525" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="I525" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J525" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="526">
-      <c r="I526" s="5"/>
+      <c r="A526" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B526" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C526" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D526" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G526" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="H526" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="I526" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J526" s="4">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="527">
-      <c r="I527" s="5"/>
+      <c r="A527" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B527" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C527" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D527" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G527" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="H527" s="4">
+        <v>9.0</v>
+      </c>
+      <c r="I527" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J527" s="4">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="528">
-      <c r="I528" s="5"/>
+      <c r="A528" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B528" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C528" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D528" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G528" s="4">
+        <v>8.0</v>
+      </c>
+      <c r="H528" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="I528" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J528" s="4">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="529">
-      <c r="I529" s="5"/>
+      <c r="A529" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B529" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C529" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D529" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="G529" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="H529" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="I529" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J529" s="4">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="530">
-      <c r="I530" s="5"/>
+      <c r="A530" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B530" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C530" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D530" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G530" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="H530" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="I530" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J530" s="4">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="531">
-      <c r="I531" s="5"/>
+      <c r="A531" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B531" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C531" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D531" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G531" s="4">
+        <v>9.0</v>
+      </c>
+      <c r="H531" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="I531" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J531" s="4">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="532">
-      <c r="I532" s="5"/>
+      <c r="A532" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B532" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C532" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D532" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G532" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="H532" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="I532" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J532" s="4">
+        <v>5.0</v>
+      </c>
     </row>
     <row r="533">
-      <c r="I533" s="5"/>
+      <c r="A533" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B533" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C533" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D533" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="G533" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H533" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="I533" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J533" s="4">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="534">
-      <c r="I534" s="5"/>
+      <c r="A534" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B534" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C534" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D534" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G534" s="4">
+        <v>8.0</v>
+      </c>
+      <c r="H534" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="I534" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J534" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="535">
-      <c r="I535" s="5"/>
+      <c r="A535" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B535" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C535" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D535" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G535" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="H535" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="I535" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J535" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="536">
-      <c r="I536" s="5"/>
+      <c r="A536" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B536" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C536" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D536" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="G536" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="H536" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="I536" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J536" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="537">
-      <c r="I537" s="5"/>
+      <c r="A537" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B537" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C537" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D537" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="G537" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="H537" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="I537" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J537" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="538">
-      <c r="I538" s="5"/>
+      <c r="A538" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B538" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C538" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D538" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G538" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H538" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="I538" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J538" s="4">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="539">
-      <c r="I539" s="5"/>
+      <c r="A539" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B539" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C539" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D539" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="G539" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="H539" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="I539" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J539" s="4">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="540">
-      <c r="I540" s="5"/>
+      <c r="A540" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B540" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C540" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D540" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G540" s="4">
+        <v>9.0</v>
+      </c>
+      <c r="H540" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="I540" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J540" s="4">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="541">
-      <c r="I541" s="5"/>
+      <c r="A541" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B541" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C541" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D541" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="G541" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="H541" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="I541" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J541" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="542">
-      <c r="I542" s="5"/>
+      <c r="A542" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B542" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C542" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D542" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G542" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="H542" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="I542" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J542" s="4">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="543">
-      <c r="I543" s="5"/>
+      <c r="A543" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B543" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C543" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D543" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G543" s="4">
+        <v>11.0</v>
+      </c>
+      <c r="H543" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="I543" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J543" s="4">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="544">
-      <c r="I544" s="5"/>
+      <c r="A544" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B544" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C544" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D544" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G544" s="4">
+        <v>8.0</v>
+      </c>
+      <c r="H544" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="I544" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J544" s="4">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="545">
-      <c r="I545" s="5"/>
+      <c r="A545" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B545" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C545" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D545" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G545" s="4">
+        <v>9.0</v>
+      </c>
+      <c r="H545" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="I545" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J545" s="4">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="546">
-      <c r="I546" s="5"/>
+      <c r="A546" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B546" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C546" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D546" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G546" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="H546" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="I546" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J546" s="4">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="547">
-      <c r="I547" s="5"/>
+      <c r="A547" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B547" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C547" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D547" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G547" s="4">
+        <v>8.5</v>
+      </c>
+      <c r="H547" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="I547" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J547" s="4">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="548">
-      <c r="I548" s="5"/>
+      <c r="A548" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B548" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C548" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D548" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G548" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="H548" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="I548" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J548" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="549">
-      <c r="I549" s="5"/>
+      <c r="A549" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B549" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C549" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D549" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G549" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="H549" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="I549" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J549" s="4">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="550">
-      <c r="I550" s="5"/>
+      <c r="A550" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B550" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C550" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D550" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G550" s="4">
+        <v>9.5</v>
+      </c>
+      <c r="H550" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="I550" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J550" s="4">
+        <v>6.0</v>
+      </c>
     </row>
     <row r="551">
-      <c r="I551" s="5"/>
+      <c r="A551" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B551" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C551" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D551" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G551" s="4">
+        <v>11.0</v>
+      </c>
+      <c r="H551" s="4">
+        <v>6.5</v>
+      </c>
+      <c r="I551" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J551" s="4">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="552">
-      <c r="I552" s="5"/>
+      <c r="A552" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B552" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C552" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D552" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G552" s="4">
+        <v>11.0</v>
+      </c>
+      <c r="H552" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="I552" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J552" s="4">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="553">
-      <c r="I553" s="5"/>
+      <c r="A553" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B553" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C553" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D553" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G553" s="4">
+        <v>14.0</v>
+      </c>
+      <c r="H553" s="4">
+        <v>9.0</v>
+      </c>
+      <c r="I553" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J553" s="4">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="554">
       <c r="I554" s="5"/>
@@ -18679,6 +20768,1526 @@
         <v>9.0</v>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C142" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D142" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G142" s="4">
+        <v>14.0</v>
+      </c>
+      <c r="H142" s="4">
+        <v>14.2</v>
+      </c>
+      <c r="I142" s="4">
+        <v>1.6</v>
+      </c>
+      <c r="J142" s="4">
+        <v>1.6</v>
+      </c>
+      <c r="K142" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="L142" s="4">
+        <v>4.8</v>
+      </c>
+      <c r="M142" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="N142" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="O142" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="P142" s="4">
+        <v>1.9</v>
+      </c>
+      <c r="Q142" s="4">
+        <v>2.4</v>
+      </c>
+      <c r="R142" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="S142" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="T142" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="U142" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="V142" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="W142" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="X142" s="4">
+        <v>3.6</v>
+      </c>
+      <c r="Y142" s="4">
+        <v>1.7</v>
+      </c>
+      <c r="Z142" s="4">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C143" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D143" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G143" s="4">
+        <v>16.0</v>
+      </c>
+      <c r="H143" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="I143" s="4">
+        <v>2.2</v>
+      </c>
+      <c r="J143" s="4">
+        <v>2.1</v>
+      </c>
+      <c r="K143" s="4">
+        <v>1.6</v>
+      </c>
+      <c r="L143" s="4">
+        <v>1.6</v>
+      </c>
+      <c r="M143" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="N143" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="O143" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="P143" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="Q143" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="R143" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="S143" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="T143" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="U143" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="V143" s="4">
+        <v>3.6</v>
+      </c>
+      <c r="W143" s="4">
+        <v>1.9</v>
+      </c>
+      <c r="X143" s="4">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C144" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D144" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G144" s="4">
+        <v>18.2</v>
+      </c>
+      <c r="H144" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="I144" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="J144" s="4">
+        <v>2.2</v>
+      </c>
+      <c r="K144" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="L144" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="M144" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="N144" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="O144" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="P144" s="4">
+        <v>1.9</v>
+      </c>
+      <c r="Q144" s="4">
+        <v>6.2</v>
+      </c>
+      <c r="R144" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="S144" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="T144" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="U144" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="V144" s="4">
+        <v>5.4</v>
+      </c>
+      <c r="W144" s="4">
+        <v>3.6</v>
+      </c>
+      <c r="X144" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="Y144" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="Z144" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="AA144" s="4">
+        <v>9.7</v>
+      </c>
+      <c r="AB144" s="4">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C145" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D145" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G145" s="4">
+        <v>17.9</v>
+      </c>
+      <c r="H145" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="I145" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="J145" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="K145" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="L145" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="M145" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="N145" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="O145" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="P145" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="Q145" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="R145" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="S145" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="T145" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="U145" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="V145" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="W145" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="X145" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="Y145" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="Z145" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="AA145" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="AB145" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="AC145" s="4">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C146" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D146" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G146" s="4">
+        <v>9.2</v>
+      </c>
+      <c r="H146" s="4">
+        <v>4.4</v>
+      </c>
+      <c r="I146" s="4">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C147" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D147" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G147" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="H147" s="4">
+        <v>6.4</v>
+      </c>
+      <c r="I147" s="4">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C148" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D148" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G148" s="4">
+        <v>12.5</v>
+      </c>
+      <c r="H148" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="I148" s="4">
+        <v>4.4</v>
+      </c>
+      <c r="J148" s="4">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C149" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D149" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="G149" s="4">
+        <v>7.9</v>
+      </c>
+      <c r="H149" s="4">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C150" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D150" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G150" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="H150" s="4">
+        <v>4.4</v>
+      </c>
+      <c r="I150" s="4">
+        <v>4.9</v>
+      </c>
+      <c r="J150" s="4">
+        <v>2.6</v>
+      </c>
+      <c r="K150" s="4">
+        <v>3.1</v>
+      </c>
+      <c r="L150" s="4">
+        <v>1.1</v>
+      </c>
+      <c r="M150" s="4">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C151" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D151" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G151" s="4">
+        <v>14.1</v>
+      </c>
+      <c r="H151" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="I151" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="J151" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="K151" s="4">
+        <v>2.1</v>
+      </c>
+      <c r="L151" s="4">
+        <v>2.1</v>
+      </c>
+      <c r="M151" s="4">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C152" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D152" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G152" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="H152" s="4">
+        <v>2.9</v>
+      </c>
+      <c r="I152" s="4">
+        <v>1.9</v>
+      </c>
+      <c r="J152" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="K152" s="4">
+        <v>2.2</v>
+      </c>
+      <c r="L152" s="4">
+        <v>1.4</v>
+      </c>
+      <c r="M152" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="N152" s="4">
+        <v>5.1</v>
+      </c>
+      <c r="O152" s="4">
+        <v>2.3</v>
+      </c>
+      <c r="P152" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="Q152" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="R152" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="S152" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="T152" s="4">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C153" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D153" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G153" s="4">
+        <v>14.9</v>
+      </c>
+      <c r="H153" s="4">
+        <v>4.9</v>
+      </c>
+      <c r="I153" s="4">
+        <v>3.3</v>
+      </c>
+      <c r="J153" s="4">
+        <v>2.1</v>
+      </c>
+      <c r="K153" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="L153" s="4">
+        <v>3.3</v>
+      </c>
+      <c r="M153" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="N153" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="O153" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="P153" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="Q153" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="R153" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="S153" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="T153" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="U153" s="4">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C154" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D154" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G154" s="4">
+        <v>13.0</v>
+      </c>
+      <c r="H154" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="I154" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="J154" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="K154" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="L154" s="4">
+        <v>2.6</v>
+      </c>
+      <c r="M154" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="N154" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="O154" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="P154" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="Q154" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="R154" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="S154" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="T154" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="U154" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="V154" s="4">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C155" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D155" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G155" s="4">
+        <v>12.9</v>
+      </c>
+      <c r="H155" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="I155" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="J155" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="K155" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="L155" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="M155" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="N155" s="4">
+        <v>3.6</v>
+      </c>
+      <c r="O155" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="P155" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="Q155" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="R155" s="4">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C156" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D156" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G156" s="4">
+        <v>8.0</v>
+      </c>
+      <c r="H156" s="4">
+        <v>8.2</v>
+      </c>
+      <c r="I156" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="J156" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="K156" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="L156" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="M156" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="N156" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="O156" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="P156" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="Q156" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="R156" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="S156" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="T156" s="4">
+        <v>1.7</v>
+      </c>
+      <c r="U156" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="V156" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="W156" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="X156" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="Y156" s="4">
+        <v>8.0</v>
+      </c>
+      <c r="Z156" s="4">
+        <v>21.0</v>
+      </c>
+      <c r="AA156" s="4">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C157" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D157" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G157" s="4">
+        <v>15.0</v>
+      </c>
+      <c r="H157" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="I157" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="J157" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="K157" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="L157" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="M157" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="N157" s="4">
+        <v>15.0</v>
+      </c>
+      <c r="O157" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="P157" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="Q157" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="R157" s="4">
+        <v>15.6</v>
+      </c>
+      <c r="S157" s="4">
+        <v>8.0</v>
+      </c>
+      <c r="T157" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="U157" s="4">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C158" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D158" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G158" s="4">
+        <v>16.0</v>
+      </c>
+      <c r="H158" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="I158" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="J158" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="K158" s="4">
+        <v>5.3</v>
+      </c>
+      <c r="L158" s="4">
+        <v>5.3</v>
+      </c>
+      <c r="M158" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="N158" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="O158" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="P158" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="Q158" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="R158" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="S158" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="T158" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="U158" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="V158" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="W158" s="4">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C159" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D159" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G159" s="4">
+        <v>9.0</v>
+      </c>
+      <c r="H159" s="4">
+        <v>4.9</v>
+      </c>
+      <c r="I159" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="J159" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="K159" s="4">
+        <v>16.0</v>
+      </c>
+      <c r="L159" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="M159" s="4">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C160" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D160" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G160" s="4">
+        <v>13.5</v>
+      </c>
+      <c r="H160" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="I160" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="J160" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="K160" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="L160" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="M160" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="N160" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="O160" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="P160" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="Q160" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="R160" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="S160" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="T160" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="U160" s="4">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C161" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D161" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G161" s="4">
+        <v>17.5</v>
+      </c>
+      <c r="H161" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="I161" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="J161" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="K161" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="L161" s="4">
+        <v>4.9</v>
+      </c>
+      <c r="M161" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="N161" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="O161" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="P161" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="Q161" s="4">
+        <v>55.0</v>
+      </c>
+      <c r="R161" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="S161" s="4">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C162" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D162" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G162" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="H162" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="I162" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="J162" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="K162" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="L162" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="M162" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="N162" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="O162" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="P162" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="Q162" s="4">
+        <v>18.0</v>
+      </c>
+      <c r="R162" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="S162" s="4">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C163" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D163" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G163" s="4">
+        <v>18.2</v>
+      </c>
+      <c r="H163" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="I163" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="J163" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="K163" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="L163" s="4">
+        <v>2.9</v>
+      </c>
+      <c r="M163" s="4">
+        <v>2.9</v>
+      </c>
+      <c r="N163" s="4">
+        <v>2.9</v>
+      </c>
+      <c r="O163" s="4">
+        <v>2.9</v>
+      </c>
+      <c r="P163" s="4">
+        <v>2.6</v>
+      </c>
+      <c r="Q163" s="4">
+        <v>3.3</v>
+      </c>
+      <c r="R163" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="S163" s="4">
+        <v>1.8</v>
+      </c>
+      <c r="T163" s="4">
+        <v>7.2</v>
+      </c>
+      <c r="U163" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="V163" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="W163" s="4">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C164" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D164" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G164" s="4">
+        <v>16.0</v>
+      </c>
+      <c r="H164" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="I164" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="J164" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="K164" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="L164" s="4">
+        <v>1.8</v>
+      </c>
+      <c r="M164" s="4">
+        <v>8.5</v>
+      </c>
+      <c r="N164" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="O164" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="P164" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="Q164" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="R164" s="4">
+        <v>6.5</v>
+      </c>
+      <c r="S164" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="T164" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="U164" s="4">
+        <v>6.7</v>
+      </c>
+      <c r="V164" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="W164" s="4">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C165" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D165" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G165" s="4">
+        <v>9.0</v>
+      </c>
+      <c r="H165" s="4">
+        <v>2.2</v>
+      </c>
+      <c r="I165" s="4">
+        <v>2.2</v>
+      </c>
+      <c r="J165" s="4">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C166" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D166" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G166" s="4">
+        <v>17.2</v>
+      </c>
+      <c r="H166" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="I166" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="J166" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="K166" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="L166" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="M166" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="N166" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="O166" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="P166" s="4">
+        <v>2.8</v>
+      </c>
+      <c r="Q166" s="4">
+        <v>8.0</v>
+      </c>
+      <c r="R166" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="S166" s="4">
+        <v>15.0</v>
+      </c>
+      <c r="T166" s="4">
+        <v>8.0</v>
+      </c>
+      <c r="U166" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="V166" s="4">
+        <v>8.0</v>
+      </c>
+      <c r="W166" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="X166" s="4">
+        <v>8.0</v>
+      </c>
+      <c r="Y166" s="4">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C167" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D167" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G167" s="4">
+        <v>15.0</v>
+      </c>
+      <c r="H167" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="I167" s="4">
+        <v>2.1</v>
+      </c>
+      <c r="J167" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="K167" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="L167" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="M167" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="N167" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="O167" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="P167" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="Q167" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="R167" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="S167" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="T167" s="4">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C168" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D168" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G168" s="4">
+        <v>12.6</v>
+      </c>
+      <c r="H168" s="4">
+        <v>5.2</v>
+      </c>
+      <c r="I168" s="4">
+        <v>1.9</v>
+      </c>
+      <c r="J168" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="K168" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="L168" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="M168" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="N168" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="O168" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="P168" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="Q168" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="R168" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="S168" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="T168" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="U168" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="V168" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="W168" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="X168" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="Y168" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="Z168" s="4">
+        <v>9.0</v>
+      </c>
+      <c r="AA168" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="AB168" s="4">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C169" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D169" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G169" s="4">
+        <v>12.6</v>
+      </c>
+      <c r="H169" s="4">
+        <v>13.5</v>
+      </c>
+      <c r="I169" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="J169" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="K169" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="L169" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="M169" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="N169" s="4">
+        <v>8.0</v>
+      </c>
+      <c r="O169" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="P169" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="Q169" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="R169" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="S169" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="T169" s="4">
+        <v>20.0</v>
+      </c>
+      <c r="U169" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="V169" s="4">
+        <v>1.0</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations>
     <dataValidation type="list" allowBlank="1" sqref="E2:E57">
@@ -26236,6 +29845,1248 @@
         <v>1.5</v>
       </c>
     </row>
+    <row r="182">
+      <c r="A182" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C182" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D182" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G182" s="4">
+        <v>17.8</v>
+      </c>
+      <c r="H182" s="4">
+        <v>5.8</v>
+      </c>
+      <c r="I182" s="4">
+        <v>1.9</v>
+      </c>
+      <c r="J182" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="K182" s="4">
+        <v>1.6</v>
+      </c>
+      <c r="L182" s="4">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C183" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D183" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G183" s="4">
+        <v>19.8</v>
+      </c>
+      <c r="H183" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="I183" s="4">
+        <v>1.9</v>
+      </c>
+      <c r="J183" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="K183" s="4">
+        <v>11.2</v>
+      </c>
+      <c r="L183" s="4">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C184" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D184" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G184" s="4">
+        <v>18.6</v>
+      </c>
+      <c r="H184" s="4">
+        <v>5.2</v>
+      </c>
+      <c r="I184" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="J184" s="4">
+        <v>1.8</v>
+      </c>
+      <c r="K184" s="4">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C185" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D185" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="G185" s="4">
+        <v>13.8</v>
+      </c>
+      <c r="H185" s="4">
+        <v>5.6</v>
+      </c>
+      <c r="I185" s="4">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C186" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D186" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G186" s="4">
+        <v>23.2</v>
+      </c>
+      <c r="H186" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="I186" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="J186" s="4">
+        <v>5.4</v>
+      </c>
+      <c r="K186" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="L186" s="4">
+        <v>1.4</v>
+      </c>
+      <c r="M186" s="4">
+        <v>6.9</v>
+      </c>
+      <c r="N186" s="4">
+        <v>56.0</v>
+      </c>
+      <c r="O186" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="P186" s="4">
+        <v>2.4</v>
+      </c>
+      <c r="Q186" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="R186" s="4">
+        <v>2.2</v>
+      </c>
+      <c r="S186" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="T186" s="4">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C187" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D187" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G187" s="4">
+        <v>11.0</v>
+      </c>
+      <c r="H187" s="4">
+        <v>7.9</v>
+      </c>
+      <c r="I187" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="J187" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="K187" s="4">
+        <v>3.3</v>
+      </c>
+      <c r="L187" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="M187" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="N187" s="4">
+        <v>2.9</v>
+      </c>
+      <c r="O187" s="4">
+        <v>6.5</v>
+      </c>
+      <c r="P187" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="Q187" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="R187" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="S187" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="T187" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="U187" s="4">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B188" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C188" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D188" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G188" s="4">
+        <v>17.1</v>
+      </c>
+      <c r="H188" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="I188" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="J188" s="4">
+        <v>6.9</v>
+      </c>
+      <c r="K188" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="L188" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="M188" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="N188" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="O188" s="4">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B189" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C189" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D189" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G189" s="4">
+        <v>14.5</v>
+      </c>
+      <c r="H189" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="I189" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="J189" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="K189" s="4">
+        <v>4.8</v>
+      </c>
+      <c r="L189" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="M189" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="N189" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="O189" s="4">
+        <v>8.1</v>
+      </c>
+      <c r="P189" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="Q189" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="R189" s="4">
+        <v>9.5</v>
+      </c>
+      <c r="S189" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="T189" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="U189" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="V189" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="W189" s="4">
+        <v>7.2</v>
+      </c>
+      <c r="X189" s="4">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B190" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C190" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D190" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G190" s="4">
+        <v>16.5</v>
+      </c>
+      <c r="H190" s="4">
+        <v>10.7</v>
+      </c>
+      <c r="I190" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="J190" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="K190" s="4">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C191" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D191" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G191" s="4">
+        <v>17.0</v>
+      </c>
+      <c r="H191" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="I191" s="4">
+        <v>1.7</v>
+      </c>
+      <c r="J191" s="4">
+        <v>8.2</v>
+      </c>
+      <c r="K191" s="4">
+        <v>8.0</v>
+      </c>
+      <c r="L191" s="4">
+        <v>8.0</v>
+      </c>
+      <c r="M191" s="4">
+        <v>6.5</v>
+      </c>
+      <c r="N191" s="4">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B192" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C192" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D192" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G192" s="4">
+        <v>14.0</v>
+      </c>
+      <c r="H192" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="I192" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="J192" s="4">
+        <v>8.1</v>
+      </c>
+      <c r="K192" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="L192" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="M192" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="N192" s="4">
+        <v>8.5</v>
+      </c>
+      <c r="O192" s="4">
+        <v>6.5</v>
+      </c>
+      <c r="P192" s="4">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C193" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D193" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G193" s="4">
+        <v>11.8</v>
+      </c>
+      <c r="H193" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="I193" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="J193" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="K193" s="4">
+        <v>10.1</v>
+      </c>
+      <c r="L193" s="4">
+        <v>5.4</v>
+      </c>
+      <c r="M193" s="4">
+        <v>6.2</v>
+      </c>
+      <c r="N193" s="4">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C194" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D194" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="G194" s="4">
+        <v>14.8</v>
+      </c>
+      <c r="H194" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="I194" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="J194" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="K194" s="4">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C195" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D195" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G195" s="4">
+        <v>15.7</v>
+      </c>
+      <c r="H195" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="I195" s="4">
+        <v>5.7</v>
+      </c>
+      <c r="J195" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="K195" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="L195" s="4">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C196" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D196" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="G196" s="4">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C197" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D197" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G197" s="4">
+        <v>17.1</v>
+      </c>
+      <c r="H197" s="4">
+        <v>9.0</v>
+      </c>
+      <c r="I197" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="J197" s="4">
+        <v>4.4</v>
+      </c>
+      <c r="K197" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="L197" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="M197" s="4">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B198" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C198" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D198" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G198" s="4">
+        <v>18.3</v>
+      </c>
+      <c r="H198" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="I198" s="4">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B199" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C199" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D199" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G199" s="4">
+        <v>18.6</v>
+      </c>
+      <c r="H199" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="I199" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="J199" s="4">
+        <v>6.5</v>
+      </c>
+      <c r="K199" s="4">
+        <v>1.9</v>
+      </c>
+      <c r="L199" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="M199" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="N199" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="O199" s="4">
+        <v>3.4</v>
+      </c>
+      <c r="P199" s="4">
+        <v>6.9</v>
+      </c>
+      <c r="Q199" s="4">
+        <v>2.1</v>
+      </c>
+      <c r="R199" s="4">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C200" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D200" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G200" s="4">
+        <v>20.5</v>
+      </c>
+      <c r="H200" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="I200" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="J200" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="K200" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="L200" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="M200" s="4">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C201" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D201" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G201" s="4">
+        <v>18.2</v>
+      </c>
+      <c r="H201" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="I201" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="J201" s="4">
+        <v>2.6</v>
+      </c>
+      <c r="K201" s="4">
+        <v>4.6</v>
+      </c>
+      <c r="L201" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="M201" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="N201" s="4">
+        <v>1.6</v>
+      </c>
+      <c r="O201" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="P201" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="Q201" s="4">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B202" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C202" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D202" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G202" s="4">
+        <v>7.8</v>
+      </c>
+      <c r="H202" s="4">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B203" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C203" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D203" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G203" s="4">
+        <v>13.8</v>
+      </c>
+      <c r="H203" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="I203" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="J203" s="4">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B204" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C204" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D204" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G204" s="4">
+        <v>10.8</v>
+      </c>
+      <c r="H204" s="4">
+        <v>4.6</v>
+      </c>
+      <c r="I204" s="4">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B205" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C205" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D205" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G205" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="H205" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="I205" s="4">
+        <v>6.5</v>
+      </c>
+      <c r="J205" s="4">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B206" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C206" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D206" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G206" s="4">
+        <v>20.4</v>
+      </c>
+      <c r="H206" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="I206" s="4">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B207" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C207" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D207" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G207" s="4">
+        <v>16.5</v>
+      </c>
+      <c r="H207" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="I207" s="4">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B208" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C208" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D208" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G208" s="4">
+        <v>21.0</v>
+      </c>
+      <c r="H208" s="4">
+        <v>6.2</v>
+      </c>
+      <c r="I208" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="J208" s="4">
+        <v>2.9</v>
+      </c>
+      <c r="K208" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="L208" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="M208" s="4">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B209" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C209" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D209" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G209" s="4">
+        <v>19.2</v>
+      </c>
+      <c r="H209" s="4">
+        <v>11.0</v>
+      </c>
+      <c r="I209" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="J209" s="4">
+        <v>2.9</v>
+      </c>
+      <c r="K209" s="4">
+        <v>1.9</v>
+      </c>
+      <c r="L209" s="4">
+        <v>1.4</v>
+      </c>
+      <c r="M209" s="4">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B210" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C210" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D210" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G210" s="4">
+        <v>20.8</v>
+      </c>
+      <c r="H210" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="I210" s="4">
+        <v>1.9</v>
+      </c>
+      <c r="J210" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="K210" s="4">
+        <v>6.7</v>
+      </c>
+      <c r="L210" s="4">
+        <v>5.3</v>
+      </c>
+      <c r="M210" s="4">
+        <v>8.7</v>
+      </c>
+      <c r="N210" s="4">
+        <v>7.4</v>
+      </c>
+      <c r="O210" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="P210" s="4">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B211" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C211" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D211" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G211" s="4">
+        <v>15.4</v>
+      </c>
+      <c r="H211" s="4">
+        <v>4.4</v>
+      </c>
+      <c r="I211" s="4">
+        <v>3.1</v>
+      </c>
+      <c r="J211" s="4">
+        <v>3.4</v>
+      </c>
+      <c r="K211" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="L211" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="M211" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="N211" s="16">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B212" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C212" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D212" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G212" s="4">
+        <v>15.5</v>
+      </c>
+      <c r="H212" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="I212" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="J212" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="K212" s="4">
+        <v>11.0</v>
+      </c>
+      <c r="L212" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="M212" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="N212" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="O212" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="P212" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="Q212" s="4">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B213" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C213" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D213" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="G213" s="4">
+        <v>14.0</v>
+      </c>
+      <c r="H213" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="I213" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="J213" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="K213" s="4">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B214" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C214" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D214" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G214" s="4">
+        <v>13.4</v>
+      </c>
+      <c r="H214" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="I214" s="4">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B215" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C215" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="D215" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G215" s="4">
+        <v>19.2</v>
+      </c>
+      <c r="H215" s="4">
+        <v>5.6</v>
+      </c>
+      <c r="I215" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="J215" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="K215" s="4">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B216" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C216" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="D216" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="G216" s="4">
+        <v>9.5</v>
+      </c>
+      <c r="H216" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="I216" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="J216" s="4">
+        <v>7.8</v>
+      </c>
+      <c r="K216" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="L216" s="4">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="6">
+        <v>44568.0</v>
+      </c>
+      <c r="B217" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C217" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="D217" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="G217" s="4">
+        <v>15.7</v>
+      </c>
+      <c r="H217" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="I217" s="4">
+        <v>8.2</v>
+      </c>
+      <c r="J217" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="K217" s="4">
+        <v>3.6</v>
+      </c>
+      <c r="L217" s="4">
+        <v>1.5</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations>
     <dataValidation type="list" allowBlank="1" sqref="E2:E73">

--- a/nursery_monitoring/GB monitoring.xlsx
+++ b/nursery_monitoring/GB monitoring.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2012" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2018" uniqueCount="115">
   <si>
     <t>Date</t>
   </si>
@@ -216,6 +216,24 @@
   </si>
   <si>
     <t>M20</t>
+  </si>
+  <si>
+    <t>M21</t>
+  </si>
+  <si>
+    <t>M22</t>
+  </si>
+  <si>
+    <t>M23</t>
+  </si>
+  <si>
+    <t>M24</t>
+  </si>
+  <si>
+    <t>M25</t>
+  </si>
+  <si>
+    <t>M26</t>
   </si>
   <si>
     <t>APRO1</t>
@@ -420,11 +438,11 @@
     <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -19070,19 +19088,31 @@
       <c r="Z1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="AA1" s="10"/>
-      <c r="AB1" s="10"/>
-      <c r="AC1" s="10"/>
-      <c r="AD1" s="10"/>
-      <c r="AE1" s="10"/>
-      <c r="AF1" s="10"/>
+      <c r="AA1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3">
         <v>44410.0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C2" s="4">
         <v>1.0</v>
@@ -19115,7 +19145,7 @@
         <v>44410.0</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C3" s="4">
         <v>2.0</v>
@@ -19139,7 +19169,7 @@
         <v>44410.0</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C4" s="4">
         <v>3.0</v>
@@ -19172,7 +19202,7 @@
         <v>44410.0</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C5" s="4">
         <v>4.0</v>
@@ -19199,7 +19229,7 @@
         <v>44410.0</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C6" s="4">
         <v>1.0</v>
@@ -19223,7 +19253,7 @@
         <v>44410.0</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C7" s="4">
         <v>2.0</v>
@@ -19247,7 +19277,7 @@
         <v>44410.0</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C8" s="4">
         <v>3.0</v>
@@ -19277,7 +19307,7 @@
         <v>44410.0</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C9" s="4">
         <v>4.0</v>
@@ -19304,7 +19334,7 @@
         <v>44410.0</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C10" s="4">
         <v>1.0</v>
@@ -19331,7 +19361,7 @@
         <v>44410.0</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C11" s="4">
         <v>2.0</v>
@@ -19355,7 +19385,7 @@
         <v>44410.0</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C12" s="4">
         <v>3.0</v>
@@ -19385,7 +19415,7 @@
         <v>44410.0</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C13" s="4">
         <v>4.0</v>
@@ -19424,7 +19454,7 @@
         <v>44410.0</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C14" s="4">
         <v>1.0</v>
@@ -19448,7 +19478,7 @@
         <v>44410.0</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C15" s="4">
         <v>2.0</v>
@@ -19472,7 +19502,7 @@
         <v>44410.0</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C16" s="4">
         <v>3.0</v>
@@ -19499,7 +19529,7 @@
         <v>44410.0</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C17" s="4">
         <v>4.0</v>
@@ -19526,7 +19556,7 @@
         <v>44410.0</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C18" s="4">
         <v>1.0</v>
@@ -19550,7 +19580,7 @@
         <v>44410.0</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C19" s="4">
         <v>2.0</v>
@@ -19580,7 +19610,7 @@
         <v>44410.0</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C20" s="4">
         <v>3.0</v>
@@ -19607,7 +19637,7 @@
         <v>44410.0</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C21" s="4">
         <v>4.0</v>
@@ -19643,7 +19673,7 @@
         <v>44410.0</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C22" s="4">
         <v>1.0</v>
@@ -19676,7 +19706,7 @@
         <v>44410.0</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C23" s="4">
         <v>2.0</v>
@@ -19700,7 +19730,7 @@
         <v>44410.0</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C24" s="4">
         <v>3.0</v>
@@ -19739,7 +19769,7 @@
         <v>44410.0</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C25" s="4">
         <v>4.0</v>
@@ -19763,7 +19793,7 @@
         <v>44410.0</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C26" s="4">
         <v>1.0</v>
@@ -19802,7 +19832,7 @@
         <v>44410.0</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C27" s="4">
         <v>2.0</v>
@@ -19832,7 +19862,7 @@
         <v>44410.0</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C28" s="4">
         <v>3.0</v>
@@ -19868,7 +19898,7 @@
         <v>44410.0</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C29" s="4">
         <v>4.0</v>
@@ -19901,7 +19931,7 @@
         <v>44441.0</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C30" s="4">
         <v>1.0</v>
@@ -19937,7 +19967,7 @@
         <v>44441.0</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C31" s="4">
         <v>2.0</v>
@@ -19961,7 +19991,7 @@
         <v>44441.0</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C32" s="4">
         <v>3.0</v>
@@ -20006,7 +20036,7 @@
         <v>44441.0</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C33" s="4">
         <v>4.0</v>
@@ -20036,7 +20066,7 @@
         <v>44441.0</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C34" s="4">
         <v>1.0</v>
@@ -20060,7 +20090,7 @@
         <v>44441.0</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C35" s="4">
         <v>2.0</v>
@@ -20090,7 +20120,7 @@
         <v>44441.0</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C36" s="4">
         <v>3.0</v>
@@ -20129,7 +20159,7 @@
         <v>44441.0</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C37" s="1">
         <v>4.0</v>
@@ -20164,7 +20194,7 @@
         <v>44441.0</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C38" s="4">
         <v>1.0</v>
@@ -20191,7 +20221,7 @@
         <v>44441.0</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C39" s="4">
         <v>2.0</v>
@@ -20215,7 +20245,7 @@
         <v>44441.0</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C40" s="4">
         <v>3.0</v>
@@ -20254,7 +20284,7 @@
         <v>44441.0</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C41" s="4">
         <v>4.0</v>
@@ -20302,7 +20332,7 @@
         <v>44441.0</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C42" s="4">
         <v>1.0</v>
@@ -20329,7 +20359,7 @@
         <v>44441.0</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C43" s="4">
         <v>2.0</v>
@@ -20356,7 +20386,7 @@
         <v>44441.0</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C44" s="4">
         <v>3.0</v>
@@ -20386,7 +20416,7 @@
         <v>44441.0</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C45" s="4">
         <v>4.0</v>
@@ -20413,7 +20443,7 @@
         <v>44441.0</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C46" s="4">
         <v>1.0</v>
@@ -20437,7 +20467,7 @@
         <v>44441.0</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C47" s="4">
         <v>2.0</v>
@@ -20470,7 +20500,7 @@
         <v>44441.0</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C48" s="4">
         <v>3.0</v>
@@ -20503,7 +20533,7 @@
         <v>44441.0</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C49" s="4">
         <v>4.0</v>
@@ -20542,7 +20572,7 @@
         <v>44441.0</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C50" s="4">
         <v>1.0</v>
@@ -20581,7 +20611,7 @@
         <v>44441.0</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C51" s="4">
         <v>2.0</v>
@@ -20608,7 +20638,7 @@
         <v>44441.0</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C52" s="4">
         <v>3.0</v>
@@ -20656,7 +20686,7 @@
         <v>44441.0</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C53" s="4">
         <v>4.0</v>
@@ -20683,7 +20713,7 @@
         <v>44441.0</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C54" s="4">
         <v>1.0</v>
@@ -20691,7 +20721,7 @@
       <c r="D54" s="4">
         <v>1.0</v>
       </c>
-      <c r="E54" s="11"/>
+      <c r="E54" s="10"/>
       <c r="G54" s="4">
         <v>6.5</v>
       </c>
@@ -20719,7 +20749,7 @@
         <v>44441.0</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C55" s="4">
         <v>2.0</v>
@@ -20727,7 +20757,7 @@
       <c r="D55" s="4">
         <v>1.0</v>
       </c>
-      <c r="E55" s="11"/>
+      <c r="E55" s="10"/>
       <c r="G55" s="4">
         <v>7.4</v>
       </c>
@@ -20746,7 +20776,7 @@
         <v>44441.0</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C56" s="4">
         <v>3.0</v>
@@ -20754,7 +20784,7 @@
       <c r="D56" s="4">
         <v>1.0</v>
       </c>
-      <c r="E56" s="11"/>
+      <c r="E56" s="10"/>
       <c r="G56" s="4">
         <v>5.5</v>
       </c>
@@ -20791,7 +20821,7 @@
         <v>44441.0</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C57" s="4">
         <v>4.0</v>
@@ -20799,7 +20829,7 @@
       <c r="D57" s="4">
         <v>1.0</v>
       </c>
-      <c r="E57" s="11"/>
+      <c r="E57" s="10"/>
       <c r="G57" s="4">
         <v>9.2</v>
       </c>
@@ -20827,7 +20857,7 @@
         <v>44476.0</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C58" s="4">
         <v>1.0</v>
@@ -20880,7 +20910,7 @@
         <v>44476.0</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C59" s="4">
         <v>2.0</v>
@@ -20927,7 +20957,7 @@
         <v>44476.0</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C60" s="4">
         <v>3.0</v>
@@ -21004,7 +21034,7 @@
         <v>44476.0</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C61" s="4">
         <v>4.0</v>
@@ -21063,7 +21093,7 @@
         <v>44476.0</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C62" s="4">
         <v>1.0</v>
@@ -21089,7 +21119,7 @@
         <v>44476.0</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C63" s="4">
         <v>2.0</v>
@@ -21115,7 +21145,7 @@
         <v>44476.0</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C64" s="4">
         <v>3.0</v>
@@ -21150,7 +21180,7 @@
         <v>44476.0</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C65" s="4">
         <v>4.0</v>
@@ -21173,7 +21203,7 @@
         <v>44476.0</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C66" s="4">
         <v>1.0</v>
@@ -21202,7 +21232,7 @@
         <v>44476.0</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C67" s="4">
         <v>2.0</v>
@@ -21231,7 +21261,7 @@
         <v>44476.0</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C68" s="4">
         <v>3.0</v>
@@ -21269,7 +21299,7 @@
         <v>44476.0</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C69" s="4">
         <v>4.0</v>
@@ -21325,7 +21355,7 @@
         <v>44476.0</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C70" s="4">
         <v>1.0</v>
@@ -21363,7 +21393,7 @@
         <v>44476.0</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C71" s="4">
         <v>2.0</v>
@@ -21404,7 +21434,7 @@
         <v>44476.0</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C72" s="4">
         <v>3.0</v>
@@ -21463,7 +21493,7 @@
         <v>44476.0</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C73" s="4">
         <v>4.0</v>
@@ -21525,7 +21555,7 @@
         <v>44476.0</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C74" s="4">
         <v>1.0</v>
@@ -21596,7 +21626,7 @@
         <v>44476.0</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C75" s="4">
         <v>2.0</v>
@@ -21661,7 +21691,7 @@
         <v>44476.0</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C76" s="4">
         <v>3.0</v>
@@ -21711,7 +21741,7 @@
         <v>44476.0</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C77" s="4">
         <v>4.0</v>
@@ -21799,7 +21829,7 @@
         <v>44476.0</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C78" s="4">
         <v>1.0</v>
@@ -21849,7 +21879,7 @@
         <v>44476.0</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C79" s="4">
         <v>2.0</v>
@@ -21884,7 +21914,7 @@
         <v>44476.0</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C80" s="4">
         <v>3.0</v>
@@ -21925,7 +21955,7 @@
         <v>44476.0</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C81" s="4">
         <v>4.0</v>
@@ -21948,7 +21978,7 @@
         <v>44476.0</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C82" s="4">
         <v>1.0</v>
@@ -22007,7 +22037,7 @@
         <v>44476.0</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C83" s="4">
         <v>2.0</v>
@@ -22045,7 +22075,7 @@
         <v>44476.0</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C84" s="4">
         <v>3.0</v>
@@ -22113,7 +22143,7 @@
         <v>44476.0</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C85" s="4">
         <v>4.0</v>
@@ -22169,7 +22199,7 @@
         <v>44504.0</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C86" s="4">
         <v>1.0</v>
@@ -22213,7 +22243,7 @@
         <v>44504.0</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C87" s="4">
         <v>2.0</v>
@@ -22260,7 +22290,7 @@
         <v>44504.0</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C88" s="4">
         <v>3.0</v>
@@ -22316,7 +22346,7 @@
         <v>44504.0</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C89" s="4">
         <v>4.0</v>
@@ -22360,7 +22390,7 @@
         <v>44504.0</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C90" s="4">
         <v>1.0</v>
@@ -22389,7 +22419,7 @@
         <v>44504.0</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C91" s="4">
         <v>2.0</v>
@@ -22412,7 +22442,7 @@
         <v>44504.0</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C92" s="4">
         <v>3.0</v>
@@ -22438,7 +22468,7 @@
         <v>44504.0</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C93" s="4">
         <v>4.0</v>
@@ -22461,7 +22491,7 @@
         <v>44504.0</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C94" s="4">
         <v>1.0</v>
@@ -22487,7 +22517,7 @@
         <v>44504.0</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C95" s="4">
         <v>2.0</v>
@@ -22522,7 +22552,7 @@
         <v>44504.0</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C96" s="4">
         <v>3.0</v>
@@ -22563,7 +22593,7 @@
         <v>44504.0</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C97" s="4">
         <v>4.0</v>
@@ -22613,7 +22643,7 @@
         <v>44504.0</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C98" s="4">
         <v>1.0</v>
@@ -22645,7 +22675,7 @@
         <v>44504.0</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C99" s="4">
         <v>2.0</v>
@@ -22677,7 +22707,7 @@
         <v>44504.0</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C100" s="4">
         <v>3.0</v>
@@ -22748,7 +22778,7 @@
         <v>44504.0</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C101" s="4">
         <v>4.0</v>
@@ -22807,7 +22837,7 @@
         <v>44504.0</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C102" s="4">
         <v>1.0</v>
@@ -22875,7 +22905,7 @@
         <v>44504.0</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C103" s="4">
         <v>2.0</v>
@@ -22928,7 +22958,7 @@
         <v>44504.0</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C104" s="4">
         <v>3.0</v>
@@ -22975,7 +23005,7 @@
         <v>44504.0</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C105" s="4">
         <v>4.0</v>
@@ -23052,7 +23082,7 @@
         <v>44504.0</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C106" s="4">
         <v>1.0</v>
@@ -23093,7 +23123,7 @@
         <v>44504.0</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C107" s="4">
         <v>2.0</v>
@@ -23128,7 +23158,7 @@
         <v>44504.0</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C108" s="4">
         <v>3.0</v>
@@ -23172,7 +23202,7 @@
         <v>44504.0</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C109" s="4">
         <v>4.0</v>
@@ -23195,7 +23225,7 @@
         <v>44504.0</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C110" s="4">
         <v>1.0</v>
@@ -23254,7 +23284,7 @@
         <v>44504.0</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C111" s="4">
         <v>2.0</v>
@@ -23292,7 +23322,7 @@
         <v>44504.0</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C112" s="4">
         <v>3.0</v>
@@ -23351,7 +23381,7 @@
         <v>44504.0</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C113" s="4">
         <v>4.0</v>
@@ -23416,7 +23446,7 @@
         <v>44531.0</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C114" s="4">
         <v>1.0</v>
@@ -23463,7 +23493,7 @@
         <v>44531.0</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C115" s="4">
         <v>2.0</v>
@@ -23516,7 +23546,7 @@
         <v>44531.0</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C116" s="4">
         <v>3.0</v>
@@ -23575,7 +23605,7 @@
         <v>44531.0</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C117" s="4">
         <v>4.0</v>
@@ -23631,7 +23661,7 @@
         <v>44531.0</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C118" s="4">
         <v>1.0</v>
@@ -23657,7 +23687,7 @@
         <v>44531.0</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C119" s="4">
         <v>2.0</v>
@@ -23680,7 +23710,7 @@
         <v>44531.0</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C120" s="4">
         <v>3.0</v>
@@ -23712,7 +23742,7 @@
         <v>44531.0</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C121" s="4">
         <v>4.0</v>
@@ -23735,7 +23765,7 @@
         <v>44531.0</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C122" s="4">
         <v>1.0</v>
@@ -23773,7 +23803,7 @@
         <v>44531.0</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C123" s="4">
         <v>2.0</v>
@@ -23808,7 +23838,7 @@
         <v>44531.0</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C124" s="4">
         <v>3.0</v>
@@ -23828,7 +23858,7 @@
       <c r="J124" s="4">
         <v>2.4</v>
       </c>
-      <c r="K124" s="12">
+      <c r="K124" s="11">
         <v>10.0</v>
       </c>
       <c r="L124" s="4">
@@ -23843,7 +23873,7 @@
         <v>44531.0</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C125" s="4">
         <v>4.0</v>
@@ -23899,7 +23929,7 @@
         <v>44531.0</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C126" s="4">
         <v>1.0</v>
@@ -23955,7 +23985,7 @@
         <v>44531.0</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C127" s="4">
         <v>2.0</v>
@@ -23996,7 +24026,7 @@
         <v>44531.0</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C128" s="4">
         <v>3.0</v>
@@ -24076,7 +24106,7 @@
         <v>44531.0</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C129" s="4">
         <v>4.0</v>
@@ -24123,7 +24153,7 @@
         <v>44531.0</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C130" s="4">
         <v>1.0</v>
@@ -24191,7 +24221,7 @@
         <v>44531.0</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C131" s="4">
         <v>2.0</v>
@@ -24247,7 +24277,7 @@
         <v>44531.0</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C132" s="4">
         <v>3.0</v>
@@ -24294,7 +24324,7 @@
         <v>44531.0</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C133" s="4">
         <v>4.0</v>
@@ -24320,7 +24350,7 @@
         <v>44531.0</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C134" s="4">
         <v>1.0</v>
@@ -24346,7 +24376,7 @@
         <v>44531.0</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C135" s="4">
         <v>2.0</v>
@@ -24366,7 +24396,7 @@
         <v>44531.0</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C136" s="4">
         <v>3.0</v>
@@ -24392,7 +24422,7 @@
         <v>44531.0</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C137" s="4">
         <v>4.0</v>
@@ -24421,7 +24451,7 @@
         <v>44531.0</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C138" s="4">
         <v>1.0</v>
@@ -24450,7 +24480,7 @@
         <v>44531.0</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C139" s="4">
         <v>2.0</v>
@@ -24479,7 +24509,7 @@
         <v>44531.0</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C140" s="4">
         <v>3.0</v>
@@ -24505,7 +24535,7 @@
       <c r="L140" s="4">
         <v>1.5</v>
       </c>
-      <c r="M140" s="11">
+      <c r="M140" s="10">
         <f>2.5*13</f>
         <v>32.5</v>
       </c>
@@ -24515,7 +24545,7 @@
         <v>44531.0</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C141" s="4">
         <v>4.0</v>
@@ -24541,7 +24571,7 @@
         <v>44568.0</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C142" s="4">
         <v>1.0</v>
@@ -24615,7 +24645,7 @@
         <v>44568.0</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C143" s="4">
         <v>2.0</v>
@@ -24683,7 +24713,7 @@
         <v>44568.0</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C144" s="4">
         <v>3.0</v>
@@ -24763,7 +24793,7 @@
         <v>44568.0</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C145" s="4">
         <v>4.0</v>
@@ -24846,7 +24876,7 @@
         <v>44568.0</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C146" s="4">
         <v>1.0</v>
@@ -24869,7 +24899,7 @@
         <v>44568.0</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C147" s="4">
         <v>2.0</v>
@@ -24892,7 +24922,7 @@
         <v>44568.0</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C148" s="4">
         <v>3.0</v>
@@ -24918,7 +24948,7 @@
         <v>44568.0</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C149" s="4">
         <v>4.0</v>
@@ -24938,7 +24968,7 @@
         <v>44568.0</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C150" s="4">
         <v>1.0</v>
@@ -24973,7 +25003,7 @@
         <v>44568.0</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C151" s="4">
         <v>2.0</v>
@@ -25008,7 +25038,7 @@
         <v>44568.0</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C152" s="4">
         <v>3.0</v>
@@ -25064,7 +25094,7 @@
         <v>44568.0</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C153" s="4">
         <v>4.0</v>
@@ -25123,7 +25153,7 @@
         <v>44568.0</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C154" s="4">
         <v>1.0</v>
@@ -25185,7 +25215,7 @@
         <v>44568.0</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C155" s="4">
         <v>2.0</v>
@@ -25235,7 +25265,7 @@
         <v>44568.0</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C156" s="4">
         <v>3.0</v>
@@ -25312,7 +25342,7 @@
         <v>44568.0</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C157" s="4">
         <v>4.0</v>
@@ -25371,7 +25401,7 @@
         <v>44568.0</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C158" s="4">
         <v>1.0</v>
@@ -25436,7 +25466,7 @@
         <v>44568.0</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C159" s="4">
         <v>2.0</v>
@@ -25471,7 +25501,7 @@
         <v>44568.0</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C160" s="4">
         <v>3.0</v>
@@ -25530,7 +25560,7 @@
         <v>44568.0</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C161" s="4">
         <v>4.0</v>
@@ -25583,7 +25613,7 @@
         <v>44568.0</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C162" s="4">
         <v>1.0</v>
@@ -25636,7 +25666,7 @@
         <v>44568.0</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C163" s="4">
         <v>2.0</v>
@@ -25701,7 +25731,7 @@
         <v>44568.0</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C164" s="4">
         <v>3.0</v>
@@ -25766,7 +25796,7 @@
         <v>44568.0</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C165" s="4">
         <v>4.0</v>
@@ -25792,7 +25822,7 @@
         <v>44568.0</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C166" s="4">
         <v>1.0</v>
@@ -25863,7 +25893,7 @@
         <v>44568.0</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C167" s="4">
         <v>2.0</v>
@@ -25919,7 +25949,7 @@
         <v>44568.0</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C168" s="4">
         <v>3.0</v>
@@ -25999,7 +26029,7 @@
         <v>44568.0</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C169" s="4">
         <v>4.0</v>
@@ -26061,7 +26091,7 @@
         <v>44593.0</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C170" s="4">
         <v>1.0</v>
@@ -26129,7 +26159,7 @@
         <v>44593.0</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C171" s="4">
         <v>2.0</v>
@@ -26188,7 +26218,7 @@
         <v>44593.0</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C172" s="4">
         <v>3.0</v>
@@ -26244,7 +26274,7 @@
         <v>44593.0</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C173" s="4">
         <v>4.0</v>
@@ -26300,7 +26330,7 @@
         <v>44593.0</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C174" s="4">
         <v>1.0</v>
@@ -26323,7 +26353,7 @@
         <v>44593.0</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C175" s="4">
         <v>2.0</v>
@@ -26346,7 +26376,7 @@
         <v>44593.0</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C176" s="4">
         <v>3.0</v>
@@ -26369,7 +26399,7 @@
         <v>44593.0</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C177" s="4">
         <v>4.0</v>
@@ -26392,7 +26422,7 @@
         <v>44593.0</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C178" s="4">
         <v>1.0</v>
@@ -26418,7 +26448,7 @@
         <v>44593.0</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C179" s="4">
         <v>2.0</v>
@@ -26447,7 +26477,7 @@
         <v>44593.0</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C180" s="4">
         <v>3.0</v>
@@ -26491,7 +26521,7 @@
         <v>44593.0</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C181" s="4">
         <v>4.0</v>
@@ -26544,7 +26574,7 @@
         <v>44593.0</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C182" s="4">
         <v>1.0</v>
@@ -26606,7 +26636,7 @@
         <v>44593.0</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C183" s="4">
         <v>2.0</v>
@@ -26656,7 +26686,7 @@
         <v>44593.0</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C184" s="4">
         <v>3.0</v>
@@ -26730,7 +26760,7 @@
         <v>44593.0</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C185" s="4">
         <v>4.0</v>
@@ -26789,7 +26819,7 @@
         <v>44593.0</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C186" s="4">
         <v>1.0</v>
@@ -26869,7 +26899,7 @@
         <v>44593.0</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C187" s="4">
         <v>2.0</v>
@@ -26925,7 +26955,7 @@
         <v>44593.0</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C188" s="4">
         <v>3.0</v>
@@ -26978,7 +27008,7 @@
         <v>44593.0</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C189" s="4">
         <v>4.0</v>
@@ -27037,7 +27067,7 @@
         <v>44593.0</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C190" s="4">
         <v>1.0</v>
@@ -27081,7 +27111,7 @@
         <v>44593.0</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C191" s="4">
         <v>2.0</v>
@@ -27134,7 +27164,7 @@
         <v>44593.0</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C192" s="4">
         <v>3.0</v>
@@ -27205,7 +27235,7 @@
         <v>44593.0</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C193" s="4">
         <v>4.0</v>
@@ -27228,7 +27258,7 @@
         <v>44593.0</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C194" s="4">
         <v>1.0</v>
@@ -27294,24 +27324,18 @@
         <v>4.0</v>
       </c>
       <c r="Z194" s="4">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
       <c r="AA194" s="4">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="AB194" s="4">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="AC194" s="4">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="AD194" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="AE194" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="AF194" s="4">
         <v>5.0</v>
       </c>
     </row>
@@ -27320,7 +27344,7 @@
         <v>44593.0</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C195" s="4">
         <v>2.0</v>
@@ -27376,7 +27400,7 @@
         <v>44593.0</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C196" s="4">
         <v>3.0</v>
@@ -27420,7 +27444,7 @@
         <v>44593.0</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C197" s="4">
         <v>4.0</v>
@@ -27482,7 +27506,7 @@
         <v>44621.0</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C198" s="4">
         <v>1.0</v>
@@ -27562,7 +27586,7 @@
         <v>44621.0</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C199" s="4">
         <v>2.0</v>
@@ -27630,7 +27654,7 @@
         <v>44621.0</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C200" s="4">
         <v>3.0</v>
@@ -27719,7 +27743,7 @@
         <v>44621.0</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C201" s="4">
         <v>4.0</v>
@@ -27784,7 +27808,7 @@
         <v>44621.0</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C202" s="4">
         <v>1.0</v>
@@ -27807,7 +27831,7 @@
         <v>44621.0</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C203" s="4">
         <v>2.0</v>
@@ -27830,7 +27854,7 @@
         <v>44621.0</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C204" s="4">
         <v>3.0</v>
@@ -27862,7 +27886,7 @@
         <v>44621.0</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C205" s="4">
         <v>4.0</v>
@@ -27885,7 +27909,7 @@
         <v>44621.0</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C206" s="4">
         <v>1.0</v>
@@ -27920,7 +27944,7 @@
         <v>44621.0</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C207" s="4">
         <v>2.0</v>
@@ -27955,7 +27979,7 @@
         <v>44621.0</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C208" s="4">
         <v>3.0</v>
@@ -27999,7 +28023,7 @@
         <v>44621.0</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C209" s="4">
         <v>4.0</v>
@@ -28049,7 +28073,7 @@
         <v>44621.0</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C210" s="4">
         <v>1.0</v>
@@ -28132,7 +28156,7 @@
         <v>44621.0</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C211" s="4">
         <v>2.0</v>
@@ -28176,7 +28200,7 @@
         <v>44621.0</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C212" s="4">
         <v>3.0</v>
@@ -28234,6 +28258,27 @@
       </c>
       <c r="W212" s="4">
         <v>3.0</v>
+      </c>
+      <c r="X212" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="Y212" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="Z212" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="AA212" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="AB212" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="AC212" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="AD212" s="4">
+        <v>5.0</v>
       </c>
     </row>
     <row r="213">
@@ -28241,7 +28286,7 @@
         <v>44621.0</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C213" s="4">
         <v>4.0</v>
@@ -28330,7 +28375,7 @@
         <v>44621.0</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C214" s="4">
         <v>1.0</v>
@@ -28422,7 +28467,7 @@
         <v>44621.0</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C215" s="4">
         <v>2.0</v>
@@ -28496,7 +28541,7 @@
         <v>44621.0</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C216" s="4">
         <v>3.0</v>
@@ -28537,16 +28582,20 @@
       <c r="Q216" s="1">
         <v>10.0</v>
       </c>
-      <c r="R216" s="10"/>
-      <c r="S216" s="10"/>
-      <c r="T216" s="10"/>
+      <c r="R216" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="S216" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="T216" s="12"/>
     </row>
     <row r="217">
       <c r="A217" s="6">
         <v>44621.0</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C217" s="4">
         <v>4.0</v>
@@ -28594,6 +28643,9 @@
         <v>16.0</v>
       </c>
       <c r="T217" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="U217" s="4">
         <v>24.0</v>
       </c>
     </row>
@@ -28602,7 +28654,7 @@
         <v>44621.0</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C218" s="4">
         <v>1.0</v>
@@ -28667,7 +28719,7 @@
         <v>44621.0</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C219" s="4">
         <v>2.0</v>
@@ -28723,7 +28775,7 @@
         <v>44621.0</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C220" s="4">
         <v>3.0</v>
@@ -28782,7 +28834,7 @@
         <v>44621.0</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C221" s="4">
         <v>4.0</v>
@@ -28811,7 +28863,7 @@
         <v>44621.0</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C222" s="4">
         <v>1.0</v>
@@ -28867,7 +28919,7 @@
         <v>44621.0</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C223" s="4">
         <v>2.0</v>
@@ -28905,7 +28957,7 @@
         <v>44621.0</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C224" s="4">
         <v>3.0</v>
@@ -28955,7 +29007,7 @@
         <v>44621.0</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C225" s="4">
         <v>4.0</v>
@@ -29002,7 +29054,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
   <cols>
-    <col hidden="1" min="5" max="6" width="14.43"/>
+    <col hidden="1" min="4" max="6" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29084,17 +29136,17 @@
       <c r="Z1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="AA1" s="10"/>
-      <c r="AB1" s="10"/>
-      <c r="AC1" s="10"/>
-      <c r="AD1" s="10"/>
+      <c r="AA1" s="12"/>
+      <c r="AB1" s="12"/>
+      <c r="AC1" s="12"/>
+      <c r="AD1" s="12"/>
     </row>
     <row r="2">
       <c r="A2" s="3">
         <v>44410.0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C2" s="4">
         <v>1.0</v>
@@ -29134,7 +29186,7 @@
         <v>44410.0</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C3" s="4">
         <v>2.0</v>
@@ -29182,7 +29234,7 @@
         <v>44410.0</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C4" s="4">
         <v>3.0</v>
@@ -29222,7 +29274,7 @@
         <v>44410.0</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C5" s="4">
         <v>4.0</v>
@@ -29262,7 +29314,7 @@
         <v>44410.0</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C6" s="4">
         <v>1.0</v>
@@ -29306,7 +29358,7 @@
         <v>44410.0</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C7" s="4">
         <v>2.0</v>
@@ -29354,7 +29406,7 @@
         <v>44410.0</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C8" s="4">
         <v>3.0</v>
@@ -29394,7 +29446,7 @@
         <v>44410.0</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C9" s="4">
         <v>4.0</v>
@@ -29442,7 +29494,7 @@
         <v>44410.0</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C10" s="4">
         <v>1.0</v>
@@ -29484,7 +29536,7 @@
         <v>44410.0</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C11" s="4">
         <v>2.0</v>
@@ -29534,7 +29586,7 @@
         <v>44410.0</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C12" s="4">
         <v>3.0</v>
@@ -29588,7 +29640,7 @@
         <v>44410.0</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C13" s="4">
         <v>4.0</v>
@@ -29632,7 +29684,7 @@
         <v>44410.0</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C14" s="4">
         <v>1.0</v>
@@ -29676,7 +29728,7 @@
         <v>44410.0</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C15" s="4">
         <v>2.0</v>
@@ -29716,7 +29768,7 @@
         <v>44410.0</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C16" s="4">
         <v>3.0</v>
@@ -29760,7 +29812,7 @@
         <v>44410.0</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C17" s="4">
         <v>4.0</v>
@@ -29802,7 +29854,7 @@
         <v>44410.0</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C18" s="4">
         <v>1.0</v>
@@ -29842,7 +29894,7 @@
         <v>44410.0</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C19" s="4">
         <v>2.0</v>
@@ -29888,7 +29940,7 @@
         <v>44410.0</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C20" s="4">
         <v>3.0</v>
@@ -29928,7 +29980,7 @@
         <v>44410.0</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C21" s="4">
         <v>4.0</v>
@@ -29976,7 +30028,7 @@
         <v>44410.0</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C22" s="4">
         <v>1.0</v>
@@ -30018,7 +30070,7 @@
         <v>44410.0</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C23" s="4">
         <v>2.0</v>
@@ -30060,7 +30112,7 @@
         <v>44410.0</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C24" s="4">
         <v>3.0</v>
@@ -30104,7 +30156,7 @@
         <v>44410.0</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C25" s="4">
         <v>4.0</v>
@@ -30148,7 +30200,7 @@
         <v>44410.0</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C26" s="4">
         <v>1.0</v>
@@ -30188,7 +30240,7 @@
         <v>44410.0</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C27" s="4">
         <v>2.0</v>
@@ -30228,7 +30280,7 @@
         <v>44410.0</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C28" s="4">
         <v>3.0</v>
@@ -30272,7 +30324,7 @@
         <v>44410.0</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C29" s="4">
         <v>4.0</v>
@@ -30314,7 +30366,7 @@
         <v>44410.0</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C30" s="4">
         <v>1.0</v>
@@ -30366,7 +30418,7 @@
         <v>44410.0</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C31" s="4">
         <v>2.0</v>
@@ -30406,7 +30458,7 @@
         <v>44410.0</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C32" s="4">
         <v>3.0</v>
@@ -30450,7 +30502,7 @@
         <v>44410.0</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C33" s="4">
         <v>4.0</v>
@@ -30498,7 +30550,7 @@
         <v>44410.0</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C34" s="4">
         <v>1.0</v>
@@ -30538,7 +30590,7 @@
         <v>44410.0</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C35" s="4">
         <v>2.0</v>
@@ -30578,7 +30630,7 @@
         <v>44410.0</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C36" s="4">
         <v>3.0</v>
@@ -30624,7 +30676,7 @@
         <v>44410.0</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C37" s="4">
         <v>4.0</v>
@@ -30666,7 +30718,7 @@
         <v>44441.0</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C38" s="4">
         <v>1.0</v>
@@ -30706,7 +30758,7 @@
         <v>44441.0</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C39" s="4">
         <v>2.0</v>
@@ -30748,7 +30800,7 @@
         <v>44441.0</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C40" s="4">
         <v>3.0</v>
@@ -30788,7 +30840,7 @@
         <v>44441.0</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C41" s="1">
         <v>4.0</v>
@@ -30830,7 +30882,7 @@
         <v>44441.0</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C42" s="4">
         <v>1.0</v>
@@ -30870,7 +30922,7 @@
         <v>44441.0</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C43" s="4">
         <v>2.0</v>
@@ -30914,7 +30966,7 @@
         <v>44441.0</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C44" s="4">
         <v>3.0</v>
@@ -30954,7 +31006,7 @@
         <v>44441.0</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C45" s="4">
         <v>4.0</v>
@@ -31000,7 +31052,7 @@
         <v>44441.0</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C46" s="4">
         <v>1.0</v>
@@ -31042,7 +31094,7 @@
         <v>44441.0</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C47" s="4">
         <v>2.0</v>
@@ -31092,7 +31144,7 @@
         <v>44441.0</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C48" s="4">
         <v>3.0</v>
@@ -31142,7 +31194,7 @@
         <v>44441.0</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C49" s="4">
         <v>4.0</v>
@@ -31186,7 +31238,7 @@
         <v>44441.0</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C50" s="1">
         <v>1.0</v>
@@ -31230,7 +31282,7 @@
         <v>44441.0</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C51" s="4">
         <v>2.0</v>
@@ -31270,7 +31322,7 @@
         <v>44441.0</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C52" s="1">
         <v>3.0</v>
@@ -31312,7 +31364,7 @@
         <v>44441.0</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C53" s="4">
         <v>4.0</v>
@@ -31354,7 +31406,7 @@
         <v>44441.0</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C54" s="4">
         <v>1.0</v>
@@ -31394,7 +31446,7 @@
         <v>44441.0</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C55" s="4">
         <v>2.0</v>
@@ -31440,7 +31492,7 @@
         <v>44441.0</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C56" s="4">
         <v>3.0</v>
@@ -31480,7 +31532,7 @@
         <v>44441.0</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C57" s="4">
         <v>4.0</v>
@@ -31528,7 +31580,7 @@
         <v>44441.0</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C58" s="4">
         <v>1.0</v>
@@ -31570,7 +31622,7 @@
         <v>44441.0</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C59" s="4">
         <v>2.0</v>
@@ -31612,7 +31664,7 @@
         <v>44441.0</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C60" s="4">
         <v>3.0</v>
@@ -31656,7 +31708,7 @@
         <v>44441.0</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C61" s="4">
         <v>4.0</v>
@@ -31700,7 +31752,7 @@
         <v>44441.0</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C62" s="4">
         <v>1.0</v>
@@ -31740,7 +31792,7 @@
         <v>44441.0</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C63" s="4">
         <v>2.0</v>
@@ -31780,7 +31832,7 @@
         <v>44441.0</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C64" s="4">
         <v>3.0</v>
@@ -31826,7 +31878,7 @@
         <v>44441.0</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C65" s="4">
         <v>4.0</v>
@@ -31868,7 +31920,7 @@
         <v>44441.0</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C66" s="4">
         <v>1.0</v>
@@ -31918,7 +31970,7 @@
         <v>44441.0</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C67" s="4">
         <v>2.0</v>
@@ -31960,7 +32012,7 @@
         <v>44441.0</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C68" s="4">
         <v>3.0</v>
@@ -32010,7 +32062,7 @@
         <v>44441.0</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C69" s="1">
         <v>4.0</v>
@@ -32060,7 +32112,7 @@
         <v>44441.0</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C70" s="4">
         <v>1.0</v>
@@ -32100,7 +32152,7 @@
         <v>44441.0</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C71" s="4">
         <v>2.0</v>
@@ -32140,7 +32192,7 @@
         <v>44441.0</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C72" s="4">
         <v>3.0</v>
@@ -32188,7 +32240,7 @@
         <v>44441.0</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C73" s="1">
         <v>4.0</v>
@@ -32232,7 +32284,7 @@
         <v>44476.0</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C74" s="4">
         <v>1.0</v>
@@ -32277,7 +32329,7 @@
         <v>44476.0</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C75" s="4">
         <v>2.0</v>
@@ -32320,7 +32372,7 @@
         <v>44476.0</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C76" s="4">
         <v>3.0</v>
@@ -32361,7 +32413,7 @@
         <v>44476.0</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C77" s="4">
         <v>4.0</v>
@@ -32400,7 +32452,7 @@
         <v>44476.0</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C78" s="4">
         <v>1.0</v>
@@ -32449,7 +32501,7 @@
         <v>44476.0</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C79" s="4">
         <v>2.0</v>
@@ -32502,7 +32554,7 @@
         <v>44476.0</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C80" s="4">
         <v>3.0</v>
@@ -32547,7 +32599,7 @@
         <v>44476.0</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C81" s="4">
         <v>4.0</v>
@@ -32612,7 +32664,7 @@
         <v>44476.0</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C82" s="4">
         <v>1.0</v>
@@ -32655,7 +32707,7 @@
         <v>44476.0</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C83" s="4">
         <v>2.0</v>
@@ -32706,7 +32758,7 @@
         <v>44476.0</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C84" s="4">
         <v>3.0</v>
@@ -32767,7 +32819,7 @@
         <v>44476.0</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C85" s="4">
         <v>4.0</v>
@@ -32814,7 +32866,7 @@
         <v>44476.0</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C86" s="4">
         <v>1.0</v>
@@ -32855,7 +32907,7 @@
         <v>44476.0</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C87" s="4">
         <v>2.0</v>
@@ -32896,7 +32948,7 @@
         <v>44476.0</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C88" s="4">
         <v>3.0</v>
@@ -32935,7 +32987,7 @@
         <v>44476.0</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C89" s="4">
         <v>4.0</v>
@@ -32980,7 +33032,7 @@
         <v>44476.0</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C90" s="4">
         <v>1.0</v>
@@ -33023,7 +33075,7 @@
         <v>44476.0</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C91" s="4">
         <v>2.0</v>
@@ -33076,7 +33128,7 @@
         <v>44476.0</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C92" s="4">
         <v>3.0</v>
@@ -33121,7 +33173,7 @@
         <v>44476.0</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C93" s="4">
         <v>4.0</v>
@@ -33178,7 +33230,7 @@
         <v>44476.0</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C94" s="4">
         <v>1.0</v>
@@ -33217,7 +33269,7 @@
         <v>44476.0</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C95" s="4">
         <v>2.0</v>
@@ -33258,7 +33310,7 @@
         <v>44476.0</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C96" s="4">
         <v>3.0</v>
@@ -33301,7 +33353,7 @@
         <v>44476.0</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C97" s="4">
         <v>4.0</v>
@@ -33342,7 +33394,7 @@
         <v>44476.0</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C98" s="4">
         <v>1.0</v>
@@ -33383,7 +33435,7 @@
         <v>44476.0</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C99" s="4">
         <v>2.0</v>
@@ -33422,7 +33474,7 @@
         <v>44476.0</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C100" s="4">
         <v>3.0</v>
@@ -33471,7 +33523,7 @@
         <v>44476.0</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C101" s="4">
         <v>4.0</v>
@@ -33514,7 +33566,7 @@
         <v>44476.0</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C102" s="4">
         <v>1.0</v>
@@ -33571,7 +33623,7 @@
         <v>44476.0</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C103" s="4">
         <v>2.0</v>
@@ -33616,7 +33668,7 @@
         <v>44476.0</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C104" s="4">
         <v>3.0</v>
@@ -33673,7 +33725,7 @@
         <v>44476.0</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C105" s="4">
         <v>4.0</v>
@@ -33720,7 +33772,7 @@
         <v>44476.0</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C106" s="4">
         <v>1.0</v>
@@ -33759,7 +33811,7 @@
         <v>44476.0</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C107" s="4">
         <v>2.0</v>
@@ -33800,7 +33852,7 @@
         <v>44476.0</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C108" s="4">
         <v>3.0</v>
@@ -33849,7 +33901,7 @@
         <v>44476.0</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C109" s="4">
         <v>4.0</v>
@@ -33890,7 +33942,7 @@
         <v>44504.0</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C110" s="4">
         <v>1.0</v>
@@ -33933,7 +33985,7 @@
         <v>44504.0</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C111" s="4">
         <v>2.0</v>
@@ -33975,7 +34027,7 @@
         <v>44504.0</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C112" s="4">
         <v>3.0</v>
@@ -34015,7 +34067,7 @@
         <v>44504.0</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C113" s="4">
         <v>4.0</v>
@@ -34053,7 +34105,7 @@
         <v>44504.0</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C114" s="4">
         <v>1.0</v>
@@ -34113,7 +34165,7 @@
         <v>44504.0</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C115" s="4">
         <v>2.0</v>
@@ -34171,7 +34223,7 @@
         <v>44504.0</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C116" s="4">
         <v>3.0</v>
@@ -34217,7 +34269,7 @@
         <v>44504.0</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C117" s="4">
         <v>4.0</v>
@@ -34277,7 +34329,7 @@
         <v>44504.0</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C118" s="4">
         <v>1.0</v>
@@ -34317,7 +34369,7 @@
         <v>44504.0</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C119" s="4">
         <v>2.0</v>
@@ -34363,7 +34415,7 @@
         <v>44504.0</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C120" s="4">
         <v>3.0</v>
@@ -34413,7 +34465,7 @@
         <v>44504.0</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C121" s="4">
         <v>4.0</v>
@@ -34461,7 +34513,7 @@
         <v>44504.0</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C122" s="4">
         <v>1.0</v>
@@ -34501,7 +34553,7 @@
         <v>44504.0</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C123" s="4">
         <v>2.0</v>
@@ -34539,7 +34591,7 @@
         <v>44504.0</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C124" s="4">
         <v>3.0</v>
@@ -34575,7 +34627,7 @@
         <v>44504.0</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C125" s="4">
         <v>4.0</v>
@@ -34619,7 +34671,7 @@
         <v>44504.0</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C126" s="4">
         <v>1.0</v>
@@ -34659,7 +34711,7 @@
         <v>44504.0</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C127" s="4">
         <v>2.0</v>
@@ -34707,7 +34759,7 @@
         <v>44504.0</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C128" s="4">
         <v>3.0</v>
@@ -34751,7 +34803,7 @@
         <v>44504.0</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C129" s="4">
         <v>4.0</v>
@@ -34801,7 +34853,7 @@
         <v>44504.0</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C130" s="4">
         <v>1.0</v>
@@ -34839,7 +34891,7 @@
         <v>44504.0</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C131" s="4">
         <v>2.0</v>
@@ -34877,7 +34929,7 @@
         <v>44504.0</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C132" s="4">
         <v>3.0</v>
@@ -34917,7 +34969,7 @@
         <v>44504.0</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C133" s="4">
         <v>4.0</v>
@@ -34959,7 +35011,7 @@
         <v>44504.0</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C134" s="4">
         <v>1.0</v>
@@ -34997,7 +35049,7 @@
         <v>44504.0</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C135" s="4">
         <v>2.0</v>
@@ -35035,7 +35087,7 @@
         <v>44504.0</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C136" s="4">
         <v>3.0</v>
@@ -35081,7 +35133,7 @@
         <v>44504.0</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C137" s="4">
         <v>4.0</v>
@@ -35123,7 +35175,7 @@
         <v>44504.0</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C138" s="4">
         <v>1.0</v>
@@ -35177,7 +35229,7 @@
         <v>44504.0</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C139" s="4">
         <v>2.0</v>
@@ -35219,7 +35271,7 @@
         <v>44504.0</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C140" s="4">
         <v>3.0</v>
@@ -35275,7 +35327,7 @@
         <v>44504.0</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C141" s="4">
         <v>4.0</v>
@@ -35321,7 +35373,7 @@
         <v>44504.0</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C142" s="4">
         <v>1.0</v>
@@ -35341,7 +35393,7 @@
         <v>44504.0</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C143" s="4">
         <v>2.0</v>
@@ -35364,7 +35416,7 @@
         <v>44504.0</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C144" s="4">
         <v>3.0</v>
@@ -35393,7 +35445,7 @@
         <v>44504.0</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C145" s="4">
         <v>4.0</v>
@@ -35422,7 +35474,7 @@
         <v>44531.0</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C146" s="4">
         <v>1.0</v>
@@ -35445,7 +35497,7 @@
         <v>44531.0</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C147" s="4">
         <v>2.0</v>
@@ -35471,7 +35523,7 @@
         <v>44531.0</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C148" s="4">
         <v>3.0</v>
@@ -35494,7 +35546,7 @@
         <v>44531.0</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C149" s="4">
         <v>4.0</v>
@@ -35514,7 +35566,7 @@
         <v>44531.0</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C150" s="4">
         <v>1.0</v>
@@ -35567,7 +35619,7 @@
         <v>44531.0</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C151" s="4">
         <v>2.0</v>
@@ -35626,7 +35678,7 @@
         <v>44531.0</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C152" s="4">
         <v>3.0</v>
@@ -35667,7 +35719,7 @@
         <v>44531.0</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C153" s="4">
         <v>4.0</v>
@@ -35729,7 +35781,7 @@
         <v>44531.0</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C154" s="4">
         <v>1.0</v>
@@ -35752,7 +35804,7 @@
         <v>44531.0</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C155" s="4">
         <v>2.0</v>
@@ -35787,7 +35839,7 @@
         <v>44531.0</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C156" s="4">
         <v>3.0</v>
@@ -35828,7 +35880,7 @@
         <v>44531.0</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C157" s="4">
         <v>4.0</v>
@@ -35869,7 +35921,7 @@
         <v>44531.0</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C158" s="4">
         <v>1.0</v>
@@ -35892,7 +35944,7 @@
         <v>44531.0</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C159" s="4">
         <v>2.0</v>
@@ -35921,7 +35973,7 @@
         <v>44531.0</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C160" s="4">
         <v>3.0</v>
@@ -35938,7 +35990,7 @@
         <v>44531.0</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C161" s="4">
         <v>4.0</v>
@@ -35964,7 +36016,7 @@
         <v>44531.0</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C162" s="4">
         <v>1.0</v>
@@ -35987,7 +36039,7 @@
         <v>44531.0</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C163" s="4">
         <v>2.0</v>
@@ -36034,7 +36086,7 @@
         <v>44531.0</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C164" s="4">
         <v>3.0</v>
@@ -36063,7 +36115,7 @@
         <v>44531.0</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C165" s="4">
         <v>4.0</v>
@@ -36107,7 +36159,7 @@
         <v>44531.0</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C166" s="4">
         <v>1.0</v>
@@ -36127,7 +36179,7 @@
         <v>44531.0</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C167" s="4">
         <v>2.0</v>
@@ -36150,7 +36202,7 @@
         <v>44531.0</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C168" s="4">
         <v>3.0</v>
@@ -36173,7 +36225,7 @@
         <v>44531.0</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C169" s="4">
         <v>4.0</v>
@@ -36199,7 +36251,7 @@
         <v>44531.0</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C170" s="4">
         <v>1.0</v>
@@ -36219,7 +36271,7 @@
         <v>44531.0</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C171" s="4">
         <v>2.0</v>
@@ -36242,7 +36294,7 @@
         <v>44531.0</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C172" s="4">
         <v>3.0</v>
@@ -36271,7 +36323,7 @@
         <v>44531.0</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C173" s="4">
         <v>4.0</v>
@@ -36300,7 +36352,7 @@
         <v>44531.0</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C174" s="4">
         <v>1.0</v>
@@ -36338,7 +36390,7 @@
         <v>44531.0</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C175" s="4">
         <v>2.0</v>
@@ -36367,7 +36419,7 @@
         <v>44531.0</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C176" s="4">
         <v>3.0</v>
@@ -36414,7 +36466,7 @@
         <v>44531.0</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C177" s="4">
         <v>4.0</v>
@@ -36446,7 +36498,7 @@
         <v>44531.0</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C178" s="4">
         <v>1.0</v>
@@ -36466,7 +36518,7 @@
         <v>44531.0</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C179" s="4">
         <v>2.0</v>
@@ -36489,7 +36541,7 @@
         <v>44531.0</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C180" s="4">
         <v>3.0</v>
@@ -36518,7 +36570,7 @@
         <v>44531.0</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C181" s="4">
         <v>4.0</v>
@@ -36547,7 +36599,7 @@
         <v>44568.0</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C182" s="4">
         <v>1.0</v>
@@ -36579,7 +36631,7 @@
         <v>44568.0</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C183" s="4">
         <v>2.0</v>
@@ -36611,7 +36663,7 @@
         <v>44568.0</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C184" s="4">
         <v>3.0</v>
@@ -36640,7 +36692,7 @@
         <v>44568.0</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C185" s="4">
         <v>4.0</v>
@@ -36663,7 +36715,7 @@
         <v>44568.0</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C186" s="4">
         <v>1.0</v>
@@ -36719,7 +36771,7 @@
         <v>44568.0</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C187" s="4">
         <v>2.0</v>
@@ -36778,7 +36830,7 @@
         <v>44568.0</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C188" s="4">
         <v>3.0</v>
@@ -36819,7 +36871,7 @@
         <v>44568.0</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C189" s="4">
         <v>4.0</v>
@@ -36887,7 +36939,7 @@
         <v>44568.0</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C190" s="4">
         <v>1.0</v>
@@ -36916,7 +36968,7 @@
         <v>44568.0</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C191" s="4">
         <v>2.0</v>
@@ -36954,7 +37006,7 @@
         <v>44568.0</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C192" s="4">
         <v>3.0</v>
@@ -36998,7 +37050,7 @@
         <v>44568.0</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C193" s="4">
         <v>4.0</v>
@@ -37036,7 +37088,7 @@
         <v>44568.0</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C194" s="4">
         <v>1.0</v>
@@ -37065,7 +37117,7 @@
         <v>44568.0</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C195" s="4">
         <v>2.0</v>
@@ -37097,7 +37149,7 @@
         <v>44568.0</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C196" s="4">
         <v>3.0</v>
@@ -37114,7 +37166,7 @@
         <v>44568.0</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C197" s="4">
         <v>4.0</v>
@@ -37149,7 +37201,7 @@
         <v>44568.0</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C198" s="4">
         <v>1.0</v>
@@ -37172,7 +37224,7 @@
         <v>44568.0</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C199" s="4">
         <v>2.0</v>
@@ -37222,7 +37274,7 @@
         <v>44568.0</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C200" s="4">
         <v>3.0</v>
@@ -37257,7 +37309,7 @@
         <v>44568.0</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C201" s="4">
         <v>4.0</v>
@@ -37304,7 +37356,7 @@
         <v>44568.0</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C202" s="4">
         <v>1.0</v>
@@ -37324,7 +37376,7 @@
         <v>44568.0</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C203" s="4">
         <v>2.0</v>
@@ -37350,7 +37402,7 @@
         <v>44568.0</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C204" s="4">
         <v>3.0</v>
@@ -37373,7 +37425,7 @@
         <v>44568.0</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C205" s="4">
         <v>4.0</v>
@@ -37399,7 +37451,7 @@
         <v>44568.0</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C206" s="4">
         <v>1.0</v>
@@ -37422,7 +37474,7 @@
         <v>44568.0</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C207" s="4">
         <v>2.0</v>
@@ -37445,7 +37497,7 @@
         <v>44568.0</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C208" s="4">
         <v>3.0</v>
@@ -37480,7 +37532,7 @@
         <v>44568.0</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C209" s="4">
         <v>4.0</v>
@@ -37515,7 +37567,7 @@
         <v>44568.0</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C210" s="4">
         <v>1.0</v>
@@ -37559,7 +37611,7 @@
         <v>44568.0</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C211" s="4">
         <v>2.0</v>
@@ -37597,7 +37649,7 @@
         <v>44568.0</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C212" s="4">
         <v>3.0</v>
@@ -37644,7 +37696,7 @@
         <v>44568.0</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C213" s="4">
         <v>4.0</v>
@@ -37673,7 +37725,7 @@
         <v>44568.0</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C214" s="4">
         <v>1.0</v>
@@ -37696,7 +37748,7 @@
         <v>44568.0</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C215" s="4">
         <v>2.0</v>
@@ -37725,7 +37777,7 @@
         <v>44568.0</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C216" s="4">
         <v>3.0</v>
@@ -37757,7 +37809,7 @@
         <v>44568.0</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C217" s="4">
         <v>4.0</v>
@@ -37789,7 +37841,7 @@
         <v>44593.0</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C218" s="4">
         <v>1.0</v>
@@ -37827,7 +37879,7 @@
         <v>44593.0</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C219" s="4">
         <v>2.0</v>
@@ -37836,7 +37888,7 @@
         <v>1.0</v>
       </c>
       <c r="G219" s="4">
-        <v>2.0</v>
+        <v>20.0</v>
       </c>
       <c r="H219" s="4">
         <v>1.4</v>
@@ -37862,7 +37914,7 @@
         <v>44593.0</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C220" s="4">
         <v>3.0</v>
@@ -37888,7 +37940,7 @@
         <v>44593.0</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C221" s="4">
         <v>4.0</v>
@@ -37911,7 +37963,7 @@
         <v>44593.0</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C222" s="4">
         <v>1.0</v>
@@ -37967,7 +38019,7 @@
         <v>44593.0</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C223" s="4">
         <v>2.0</v>
@@ -38029,7 +38081,7 @@
         <v>44593.0</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C224" s="4">
         <v>3.0</v>
@@ -38064,7 +38116,7 @@
         <v>44593.0</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C225" s="4">
         <v>4.0</v>
@@ -38114,7 +38166,7 @@
         <v>44593.0</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C226" s="4">
         <v>1.0</v>
@@ -38149,7 +38201,7 @@
         <v>44593.0</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C227" s="4">
         <v>2.0</v>
@@ -38184,7 +38236,7 @@
         <v>44593.0</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C228" s="4">
         <v>3.0</v>
@@ -38225,7 +38277,7 @@
         <v>44593.0</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C229" s="4">
         <v>4.0</v>
@@ -38257,7 +38309,7 @@
         <v>44593.0</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C230" s="4">
         <v>1.0</v>
@@ -38292,7 +38344,7 @@
         <v>44593.0</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C231" s="4">
         <v>2.0</v>
@@ -38304,7 +38356,7 @@
         <v>16.2</v>
       </c>
       <c r="H231" s="4">
-        <v>1.4</v>
+        <v>7.4</v>
       </c>
       <c r="I231" s="4">
         <v>6.7</v>
@@ -38333,7 +38385,7 @@
         <v>44593.0</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C232" s="4">
         <v>3.0</v>
@@ -38350,7 +38402,7 @@
         <v>44593.0</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C233" s="4">
         <v>4.0</v>
@@ -38368,7 +38420,7 @@
         <v>9.0</v>
       </c>
       <c r="J233" s="4">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="234">
@@ -38376,7 +38428,7 @@
         <v>44593.0</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C234" s="4">
         <v>1.0</v>
@@ -38398,6 +38450,9 @@
       </c>
       <c r="K234" s="4">
         <v>3.0</v>
+      </c>
+      <c r="L234" s="4">
+        <v>6.0</v>
       </c>
     </row>
     <row r="235">
@@ -38405,7 +38460,7 @@
         <v>44593.0</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C235" s="4">
         <v>2.0</v>
@@ -38455,7 +38510,7 @@
         <v>44593.0</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C236" s="4">
         <v>3.0</v>
@@ -38490,7 +38545,7 @@
         <v>44593.0</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C237" s="4">
         <v>4.0</v>
@@ -38531,7 +38586,7 @@
         <v>44593.0</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C238" s="4">
         <v>1.0</v>
@@ -38548,7 +38603,7 @@
         <v>44593.0</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C239" s="4">
         <v>2.0</v>
@@ -38571,7 +38626,7 @@
         <v>44593.0</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C240" s="4">
         <v>3.0</v>
@@ -38594,7 +38649,7 @@
         <v>44593.0</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C241" s="4">
         <v>4.0</v>
@@ -38620,7 +38675,7 @@
         <v>44593.0</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C242" s="4">
         <v>1.0</v>
@@ -38643,7 +38698,7 @@
         <v>44593.0</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C243" s="4">
         <v>2.0</v>
@@ -38669,7 +38724,7 @@
         <v>44593.0</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C244" s="4">
         <v>3.0</v>
@@ -38701,7 +38756,7 @@
         <v>44593.0</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C245" s="4">
         <v>4.0</v>
@@ -38736,7 +38791,7 @@
         <v>44593.0</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C246" s="4">
         <v>1.0</v>
@@ -38783,7 +38838,7 @@
         <v>44593.0</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C247" s="4">
         <v>2.0</v>
@@ -38827,7 +38882,7 @@
         <v>44593.0</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C248" s="4">
         <v>3.0</v>
@@ -38871,7 +38926,7 @@
         <v>44593.0</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C249" s="4">
         <v>4.0</v>
@@ -38903,7 +38958,7 @@
         <v>44593.0</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C250" s="4">
         <v>1.0</v>
@@ -38926,7 +38981,7 @@
         <v>44593.0</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C251" s="4">
         <v>2.0</v>
@@ -38941,10 +38996,13 @@
         <v>5.5</v>
       </c>
       <c r="I251" s="4">
-        <v>34.0</v>
+        <v>3.4</v>
       </c>
       <c r="J251" s="4">
         <v>3.5</v>
+      </c>
+      <c r="K251" s="4">
+        <v>1.0</v>
       </c>
     </row>
     <row r="252">
@@ -38952,7 +39010,7 @@
         <v>44593.0</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C252" s="4">
         <v>3.0</v>
@@ -38978,7 +39036,7 @@
         <v>44593.0</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C253" s="4">
         <v>4.0</v>
@@ -39010,7 +39068,7 @@
         <v>44621.0</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C254" s="4">
         <v>1.0</v>
@@ -39038,6 +39096,9 @@
       </c>
       <c r="M254" s="4">
         <v>1.2</v>
+      </c>
+      <c r="N254" s="4">
+        <v>2.0</v>
       </c>
     </row>
     <row r="255">
@@ -39045,7 +39106,7 @@
         <v>44621.0</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C255" s="4">
         <v>2.0</v>
@@ -39089,7 +39150,7 @@
         <v>44621.0</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C256" s="4">
         <v>3.0</v>
@@ -39124,7 +39185,7 @@
         <v>44621.0</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C257" s="4">
         <v>4.0</v>
@@ -39147,7 +39208,7 @@
         <v>44621.0</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C258" s="4">
         <v>1.0</v>
@@ -39215,7 +39276,7 @@
         <v>44621.0</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C259" s="4">
         <v>2.0</v>
@@ -39275,6 +39336,9 @@
         <v>3.0</v>
       </c>
       <c r="X259" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="Y259" s="4">
         <v>3.0</v>
       </c>
     </row>
@@ -39283,7 +39347,7 @@
         <v>44621.0</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C260" s="4">
         <v>3.0</v>
@@ -39330,7 +39394,7 @@
         <v>44621.0</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C261" s="4">
         <v>4.0</v>
@@ -39395,7 +39459,7 @@
         <v>44621.0</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C262" s="4">
         <v>1.0</v>
@@ -39433,7 +39497,7 @@
         <v>44621.0</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C263" s="4">
         <v>2.0</v>
@@ -39480,7 +39544,7 @@
         <v>44621.0</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C264" s="4">
         <v>3.0</v>
@@ -39530,7 +39594,7 @@
         <v>44621.0</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C265" s="4">
         <v>4.0</v>
@@ -39568,7 +39632,7 @@
         <v>44621.0</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C266" s="4">
         <v>1.0</v>
@@ -39600,7 +39664,7 @@
         <v>44621.0</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C267" s="4">
         <v>2.0</v>
@@ -39635,7 +39699,7 @@
         <v>44621.0</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C268" s="4">
         <v>3.0</v>
@@ -39655,7 +39719,7 @@
         <v>44621.0</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C269" s="4">
         <v>4.0</v>
@@ -39696,7 +39760,7 @@
         <v>44621.0</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C270" s="4">
         <v>1.0</v>
@@ -39728,7 +39792,7 @@
         <v>44621.0</v>
       </c>
       <c r="B271" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C271" s="4">
         <v>2.0</v>
@@ -39784,7 +39848,7 @@
         <v>44621.0</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C272" s="4">
         <v>3.0</v>
@@ -39813,7 +39877,7 @@
         <v>44621.0</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C273" s="4">
         <v>4.0</v>
@@ -39863,7 +39927,7 @@
         <v>44621.0</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C274" s="4">
         <v>1.0</v>
@@ -39883,7 +39947,7 @@
         <v>44621.0</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C275" s="4">
         <v>2.0</v>
@@ -39915,7 +39979,7 @@
         <v>44621.0</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C276" s="4">
         <v>3.0</v>
@@ -39944,7 +40008,7 @@
         <v>44621.0</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C277" s="4">
         <v>4.0</v>
@@ -39970,7 +40034,7 @@
         <v>44621.0</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C278" s="4">
         <v>1.0</v>
@@ -39993,7 +40057,7 @@
         <v>44621.0</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C279" s="4">
         <v>2.0</v>
@@ -40016,7 +40080,7 @@
         <v>44621.0</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C280" s="4">
         <v>3.0</v>
@@ -40054,7 +40118,7 @@
         <v>44621.0</v>
       </c>
       <c r="B281" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C281" s="4">
         <v>4.0</v>
@@ -40086,7 +40150,7 @@
         <v>44621.0</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C282" s="4">
         <v>1.0</v>
@@ -40151,7 +40215,7 @@
         <v>44621.0</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C283" s="4">
         <v>2.0</v>
@@ -40192,7 +40256,7 @@
         <v>44621.0</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C284" s="4">
         <v>3.0</v>
@@ -40245,7 +40309,7 @@
         <v>44621.0</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C285" s="4">
         <v>4.0</v>
@@ -40277,7 +40341,7 @@
         <v>44621.0</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C286" s="4">
         <v>1.0</v>
@@ -40297,7 +40361,7 @@
         <v>44621.0</v>
       </c>
       <c r="B287" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C287" s="4">
         <v>2.0</v>
@@ -40320,7 +40384,7 @@
         <v>44621.0</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C288" s="4">
         <v>3.0</v>
@@ -40355,7 +40419,7 @@
         <v>44621.0</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C289" s="4">
         <v>4.0</v>
@@ -40409,36 +40473,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>10</v>
@@ -40454,7 +40518,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="I2" s="16">
         <f>MEDIAN(E2:E24)</f>
@@ -40471,7 +40535,7 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>12</v>
@@ -40487,7 +40551,7 @@
         <v>0.8</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="I3" s="16">
         <f>MEDIAN(E25:E31)</f>
@@ -40503,7 +40567,7 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>13</v>
@@ -40519,7 +40583,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="I4" s="16">
         <f>MEDIAN(E32:E40)</f>
@@ -40535,7 +40599,7 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>14</v>
@@ -40553,7 +40617,7 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>15</v>
@@ -40571,7 +40635,7 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>16</v>
@@ -40589,7 +40653,7 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>17</v>
@@ -40607,7 +40671,7 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>18</v>
@@ -40625,7 +40689,7 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>19</v>
@@ -40643,7 +40707,7 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>20</v>
@@ -40661,7 +40725,7 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>21</v>
@@ -40679,7 +40743,7 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>22</v>
@@ -40697,7 +40761,7 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>23</v>
@@ -40715,7 +40779,7 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>24</v>
@@ -40733,7 +40797,7 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>25</v>
@@ -40751,7 +40815,7 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>26</v>
@@ -40769,7 +40833,7 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>27</v>
@@ -40787,7 +40851,7 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>28</v>
@@ -40805,7 +40869,7 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>29</v>
@@ -40823,7 +40887,7 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>30</v>
@@ -40841,7 +40905,7 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>31</v>
@@ -40859,7 +40923,7 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>32</v>
@@ -40877,7 +40941,7 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>33</v>
@@ -40895,10 +40959,10 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C25" s="4">
         <v>4.0</v>
@@ -40913,10 +40977,10 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C26" s="4">
         <v>5.0</v>
@@ -40931,10 +40995,10 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C27" s="4">
         <v>4.0</v>
@@ -40949,10 +41013,10 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C28" s="4">
         <v>4.0</v>
@@ -40967,10 +41031,10 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C29" s="4">
         <v>4.0</v>
@@ -40985,10 +41049,10 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C30" s="4">
         <v>4.0</v>
@@ -41003,10 +41067,10 @@
     </row>
     <row r="31">
       <c r="A31" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C31" s="4">
         <v>4.0</v>
@@ -41021,10 +41085,10 @@
     </row>
     <row r="32">
       <c r="A32" s="4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C32" s="4">
         <v>5.0</v>
@@ -41039,10 +41103,10 @@
     </row>
     <row r="33">
       <c r="A33" s="4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C33" s="4">
         <v>4.0</v>
@@ -41057,10 +41121,10 @@
     </row>
     <row r="34">
       <c r="A34" s="4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C34" s="4">
         <v>4.0</v>
@@ -41075,10 +41139,10 @@
     </row>
     <row r="35">
       <c r="A35" s="4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C35" s="4">
         <v>6.0</v>
@@ -41093,10 +41157,10 @@
     </row>
     <row r="36">
       <c r="A36" s="4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C36" s="4">
         <v>4.0</v>
@@ -41111,10 +41175,10 @@
     </row>
     <row r="37">
       <c r="A37" s="4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C37" s="4">
         <v>4.0</v>
@@ -41129,10 +41193,10 @@
     </row>
     <row r="38">
       <c r="A38" s="4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C38" s="4">
         <v>4.0</v>
@@ -41147,10 +41211,10 @@
     </row>
     <row r="39">
       <c r="A39" s="4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C39" s="4">
         <v>5.0</v>
@@ -41165,10 +41229,10 @@
     </row>
     <row r="40">
       <c r="A40" s="4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C40" s="4">
         <v>5.0</v>
